--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_100/per_file_predictions_epoch_100.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_100/per_file_predictions_epoch_100.xlsx
@@ -808,769 +808,769 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9467,0.0073,0.0276,0.0014</t>
-  </si>
-  <si>
-    <t>0.9086,0.0127,0.0225,0.0068</t>
-  </si>
-  <si>
-    <t>0.9166,0.0207,0.0269,0.0044</t>
-  </si>
-  <si>
-    <t>0.8687,0.0308,0.0245,0.0105</t>
-  </si>
-  <si>
-    <t>0.7159,0.1877,0.0601,0.0092</t>
-  </si>
-  <si>
-    <t>0.6892,0.0903,0.0479,0.0350</t>
-  </si>
-  <si>
-    <t>0.8462,0.0340,0.0461,0.0121</t>
-  </si>
-  <si>
-    <t>0.8095,0.0948,0.0245,0.0038</t>
-  </si>
-  <si>
-    <t>0.8830,0.0294,0.0339,0.0061</t>
-  </si>
-  <si>
-    <t>0.8760,0.0169,0.0152,0.0227</t>
-  </si>
-  <si>
-    <t>0.7814,0.1000,0.0624,0.0084</t>
-  </si>
-  <si>
-    <t>0.7174,0.1723,0.0382,0.0124</t>
-  </si>
-  <si>
-    <t>0.9545,0.0074,0.0385,0.0001</t>
-  </si>
-  <si>
-    <t>0.9697,0.0072,0.0154,0.0001</t>
-  </si>
-  <si>
-    <t>0.9768,0.0034,0.0183,0.0001</t>
-  </si>
-  <si>
-    <t>0.9193,0.0085,0.0903,0.0002</t>
-  </si>
-  <si>
-    <t>0.8550,0.1448,0.0280,0.0014</t>
-  </si>
-  <si>
-    <t>0.6356,0.4144,0.0407,0.0012</t>
-  </si>
-  <si>
-    <t>0.2721,0.7778,0.0961,0.0008</t>
-  </si>
-  <si>
-    <t>0.5479,0.3037,0.0718,0.0152</t>
-  </si>
-  <si>
-    <t>0.5245,0.5334,0.0919,0.0013</t>
-  </si>
-  <si>
-    <t>0.0727,0.9414,0.0918,0.0011</t>
-  </si>
-  <si>
-    <t>0.9635,0.0015,0.0382,0.0002</t>
-  </si>
-  <si>
-    <t>0.9705,0.0168,0.0071,0.0001</t>
-  </si>
-  <si>
-    <t>0.8492,0.0060,0.2046,0.0002</t>
-  </si>
-  <si>
-    <t>0.9604,0.0040,0.0338,0.0001</t>
-  </si>
-  <si>
-    <t>0.9623,0.0018,0.0454,0.0001</t>
-  </si>
-  <si>
-    <t>0.9405,0.0055,0.0440,0.0004</t>
-  </si>
-  <si>
-    <t>0.6057,0.0211,0.5000,0.0018</t>
-  </si>
-  <si>
-    <t>0.7320,0.2499,0.0810,0.0028</t>
-  </si>
-  <si>
-    <t>0.8293,0.0931,0.0460,0.0026</t>
-  </si>
-  <si>
-    <t>0.0564,0.1833,0.9419,0.0014</t>
-  </si>
-  <si>
-    <t>0.8179,0.0902,0.1116,0.0014</t>
-  </si>
-  <si>
-    <t>0.7532,0.1235,0.0708,0.0087</t>
-  </si>
-  <si>
-    <t>0.8209,0.0796,0.0709,0.0039</t>
-  </si>
-  <si>
-    <t>0.8386,0.1341,0.0447,0.0021</t>
-  </si>
-  <si>
-    <t>0.6655,0.3569,0.0734,0.0027</t>
-  </si>
-  <si>
-    <t>0.5613,0.3141,0.0267,0.0001</t>
-  </si>
-  <si>
-    <t>0.9459,0.0021,0.0692,0.0001</t>
-  </si>
-  <si>
-    <t>0.9653,0.0006,0.0444,0.0000</t>
-  </si>
-  <si>
-    <t>0.9632,0.0024,0.0340,0.0002</t>
-  </si>
-  <si>
-    <t>0.9107,0.0170,0.0644,0.0004</t>
-  </si>
-  <si>
-    <t>0.6846,0.1579,0.0946,0.0007</t>
-  </si>
-  <si>
-    <t>0.9759,0.0015,0.0180,0.0002</t>
-  </si>
-  <si>
-    <t>0.9759,0.0071,0.0044,0.0006</t>
-  </si>
-  <si>
-    <t>0.9315,0.0426,0.0125,0.0003</t>
-  </si>
-  <si>
-    <t>0.5132,0.6389,0.0359,0.0003</t>
-  </si>
-  <si>
-    <t>0.4962,0.6497,0.0565,0.0008</t>
-  </si>
-  <si>
-    <t>0.6648,0.0091,0.4181,0.0001</t>
-  </si>
-  <si>
-    <t>0.4139,0.0366,0.6761,0.0004</t>
-  </si>
-  <si>
-    <t>0.9415,0.0049,0.0596,0.0003</t>
-  </si>
-  <si>
-    <t>0.8825,0.0185,0.1154,0.0006</t>
-  </si>
-  <si>
-    <t>0.8057,0.0221,0.2216,0.0002</t>
-  </si>
-  <si>
-    <t>0.7636,0.0211,0.2215,0.0001</t>
-  </si>
-  <si>
-    <t>0.8026,0.0922,0.0716,0.0062</t>
-  </si>
-  <si>
-    <t>0.7444,0.1258,0.0907,0.0109</t>
-  </si>
-  <si>
-    <t>0.6761,0.1320,0.0838,0.0214</t>
-  </si>
-  <si>
-    <t>0.5326,0.0368,0.6457,0.0012</t>
-  </si>
-  <si>
-    <t>0.6489,0.1485,0.0496,0.0189</t>
-  </si>
-  <si>
-    <t>0.8112,0.0219,0.0110,0.0413</t>
-  </si>
-  <si>
-    <t>0.6751,0.2930,0.0785,0.0052</t>
-  </si>
-  <si>
-    <t>0.4628,0.2493,0.1326,0.0002</t>
-  </si>
-  <si>
-    <t>0.7126,0.0237,0.2897,0.0006</t>
-  </si>
-  <si>
-    <t>0.8236,0.0107,0.2022,0.0016</t>
-  </si>
-  <si>
-    <t>0.3822,0.2406,0.3786,0.0002</t>
-  </si>
-  <si>
-    <t>0.6675,0.0033,0.5406,0.0006</t>
-  </si>
-  <si>
-    <t>0.6511,0.3969,0.0759,0.0013</t>
-  </si>
-  <si>
-    <t>0.1350,0.9157,0.0213,0.0001</t>
-  </si>
-  <si>
-    <t>0.8548,0.0691,0.0573,0.0029</t>
-  </si>
-  <si>
-    <t>0.9608,0.0098,0.0061,0.0009</t>
-  </si>
-  <si>
-    <t>0.2638,0.7789,0.0620,0.0027</t>
-  </si>
-  <si>
-    <t>0.5723,0.1033,0.3839,0.0003</t>
-  </si>
-  <si>
-    <t>0.5818,0.1808,0.1053,0.0001</t>
-  </si>
-  <si>
-    <t>0.5773,0.3921,0.0311,0.0000</t>
-  </si>
-  <si>
-    <t>0.9774,0.0023,0.0183,0.0002</t>
-  </si>
-  <si>
-    <t>0.8553,0.0707,0.0493,0.0014</t>
-  </si>
-  <si>
-    <t>0.8766,0.0361,0.0476,0.0050</t>
-  </si>
-  <si>
-    <t>0.9788,0.0031,0.0038,0.0009</t>
-  </si>
-  <si>
-    <t>0.9764,0.0093,0.0044,0.0002</t>
-  </si>
-  <si>
-    <t>0.9335,0.0217,0.0197,0.0013</t>
-  </si>
-  <si>
-    <t>0.9457,0.0144,0.0180,0.0012</t>
-  </si>
-  <si>
-    <t>0.8791,0.0262,0.0761,0.0004</t>
-  </si>
-  <si>
-    <t>0.6675,0.0356,0.3121,0.0002</t>
-  </si>
-  <si>
-    <t>0.7028,0.1174,0.1014,0.0003</t>
-  </si>
-  <si>
-    <t>0.9361,0.0053,0.0733,0.0001</t>
-  </si>
-  <si>
-    <t>0.8683,0.0128,0.1327,0.0001</t>
-  </si>
-  <si>
-    <t>0.9033,0.0056,0.1433,0.0001</t>
-  </si>
-  <si>
-    <t>0.7325,0.0437,0.0270,0.0483</t>
-  </si>
-  <si>
-    <t>0.8518,0.0294,0.0522,0.0110</t>
-  </si>
-  <si>
-    <t>0.6642,0.1721,0.0714,0.0234</t>
-  </si>
-  <si>
-    <t>0.8246,0.0375,0.0297,0.0222</t>
-  </si>
-  <si>
-    <t>0.7824,0.0679,0.0391,0.0133</t>
-  </si>
-  <si>
-    <t>0.8195,0.0197,0.0125,0.0402</t>
-  </si>
-  <si>
-    <t>0.7275,0.2100,0.0568,0.0053</t>
-  </si>
-  <si>
-    <t>0.7858,0.0649,0.0322,0.0193</t>
-  </si>
-  <si>
-    <t>0.8035,0.0686,0.0277,0.0145</t>
-  </si>
-  <si>
-    <t>0.7330,0.1111,0.0426,0.0166</t>
-  </si>
-  <si>
-    <t>0.7575,0.0508,0.0536,0.0414</t>
-  </si>
-  <si>
-    <t>0.8201,0.0403,0.0212,0.0243</t>
-  </si>
-  <si>
-    <t>0.7782,0.0661,0.0540,0.0192</t>
-  </si>
-  <si>
-    <t>0.8249,0.0847,0.0379,0.0061</t>
-  </si>
-  <si>
-    <t>0.6872,0.0955,0.0377,0.0270</t>
-  </si>
-  <si>
-    <t>0.7531,0.0500,0.0384,0.0257</t>
-  </si>
-  <si>
-    <t>0.6161,0.0160,0.4959,0.0013</t>
-  </si>
-  <si>
-    <t>0.9577,0.0021,0.0537,0.0001</t>
-  </si>
-  <si>
-    <t>0.9568,0.0118,0.0209,0.0002</t>
-  </si>
-  <si>
-    <t>0.9184,0.0142,0.0658,0.0004</t>
-  </si>
-  <si>
-    <t>0.3646,0.7265,0.0770,0.0015</t>
-  </si>
-  <si>
-    <t>0.4300,0.5508,0.1620,0.0056</t>
-  </si>
-  <si>
-    <t>0.6863,0.3146,0.0643,0.0027</t>
-  </si>
-  <si>
-    <t>0.6748,0.2483,0.0713,0.0082</t>
-  </si>
-  <si>
-    <t>0.4630,0.5571,0.1023,0.0080</t>
-  </si>
-  <si>
-    <t>0.1830,0.8534,0.1169,0.0016</t>
-  </si>
-  <si>
-    <t>0.7043,0.2770,0.0798,0.0049</t>
-  </si>
-  <si>
-    <t>0.9328,0.0348,0.0207,0.0008</t>
-  </si>
-  <si>
-    <t>0.9306,0.0292,0.0260,0.0004</t>
-  </si>
-  <si>
-    <t>0.9305,0.0158,0.0251,0.0010</t>
-  </si>
-  <si>
-    <t>0.9776,0.0042,0.0101,0.0002</t>
-  </si>
-  <si>
-    <t>0.8740,0.0384,0.0633,0.0038</t>
-  </si>
-  <si>
-    <t>0.4153,0.7547,0.0292,0.0002</t>
-  </si>
-  <si>
-    <t>0.4067,0.6779,0.0898,0.0016</t>
-  </si>
-  <si>
-    <t>0.7472,0.2626,0.0502,0.0008</t>
-  </si>
-  <si>
-    <t>0.0261,0.9602,0.2992,0.0006</t>
-  </si>
-  <si>
-    <t>0.7658,0.2273,0.0349,0.0013</t>
-  </si>
-  <si>
-    <t>0.6956,0.1798,0.0755,0.0110</t>
-  </si>
-  <si>
-    <t>0.8272,0.0549,0.0390,0.0092</t>
-  </si>
-  <si>
-    <t>0.9346,0.0265,0.0154,0.0022</t>
-  </si>
-  <si>
-    <t>0.8701,0.0447,0.0312,0.0063</t>
-  </si>
-  <si>
-    <t>0.7379,0.1146,0.0716,0.0141</t>
-  </si>
-  <si>
-    <t>0.8622,0.0469,0.0235,0.0072</t>
-  </si>
-  <si>
-    <t>0.9361,0.0113,0.0194,0.0044</t>
-  </si>
-  <si>
-    <t>0.7924,0.0746,0.0596,0.0141</t>
-  </si>
-  <si>
-    <t>0.8191,0.0578,0.0518,0.0109</t>
-  </si>
-  <si>
-    <t>0.7147,0.1542,0.1045,0.0094</t>
-  </si>
-  <si>
-    <t>0.9443,0.0032,0.0624,0.0000</t>
-  </si>
-  <si>
-    <t>0.7564,0.0399,0.1389,0.0001</t>
-  </si>
-  <si>
-    <t>0.8478,0.0071,0.2144,0.0003</t>
-  </si>
-  <si>
-    <t>0.9574,0.0030,0.0457,0.0001</t>
-  </si>
-  <si>
-    <t>0.9320,0.0193,0.0401,0.0005</t>
-  </si>
-  <si>
-    <t>0.9573,0.0115,0.0239,0.0001</t>
-  </si>
-  <si>
-    <t>0.8406,0.0099,0.2638,0.0005</t>
-  </si>
-  <si>
-    <t>0.9630,0.0066,0.0197,0.0002</t>
-  </si>
-  <si>
-    <t>0.9526,0.0105,0.0200,0.0014</t>
-  </si>
-  <si>
-    <t>0.9003,0.0110,0.0193,0.0141</t>
-  </si>
-  <si>
-    <t>0.9185,0.0142,0.0249,0.0027</t>
-  </si>
-  <si>
-    <t>0.9292,0.0143,0.0246,0.0014</t>
-  </si>
-  <si>
-    <t>0.9027,0.0059,0.1348,0.0003</t>
-  </si>
-  <si>
-    <t>0.6814,0.1998,0.0623,0.0108</t>
-  </si>
-  <si>
-    <t>0.7243,0.1756,0.0603,0.0097</t>
-  </si>
-  <si>
-    <t>0.7652,0.1092,0.0489,0.0153</t>
-  </si>
-  <si>
-    <t>0.7989,0.1934,0.0465,0.0026</t>
-  </si>
-  <si>
-    <t>0.8372,0.0342,0.1389,0.0015</t>
-  </si>
-  <si>
-    <t>0.9098,0.0317,0.0289,0.0022</t>
-  </si>
-  <si>
-    <t>0.7004,0.0949,0.0301,0.0191</t>
-  </si>
-  <si>
-    <t>0.2423,0.2014,0.7085,0.0259</t>
-  </si>
-  <si>
-    <t>0.6893,0.1314,0.0265,0.0192</t>
-  </si>
-  <si>
-    <t>0.7805,0.0804,0.0591,0.0108</t>
-  </si>
-  <si>
-    <t>0.7320,0.2148,0.0933,0.0031</t>
-  </si>
-  <si>
-    <t>0.9170,0.0147,0.0273,0.0034</t>
-  </si>
-  <si>
-    <t>0.8505,0.1350,0.0413,0.0005</t>
-  </si>
-  <si>
-    <t>0.7505,0.2344,0.0859,0.0014</t>
-  </si>
-  <si>
-    <t>0.7887,0.1144,0.0816,0.0018</t>
-  </si>
-  <si>
-    <t>0.9116,0.0523,0.0307,0.0004</t>
-  </si>
-  <si>
-    <t>0.7367,0.1477,0.0405,0.0135</t>
-  </si>
-  <si>
-    <t>0.8210,0.1048,0.0377,0.0058</t>
-  </si>
-  <si>
-    <t>0.8155,0.0283,0.0345,0.0234</t>
-  </si>
-  <si>
-    <t>0.7268,0.0738,0.0618,0.0388</t>
-  </si>
-  <si>
-    <t>0.7725,0.1535,0.0600,0.0062</t>
-  </si>
-  <si>
-    <t>0.8537,0.0257,0.0339,0.0158</t>
-  </si>
-  <si>
-    <t>0.7713,0.0661,0.0482,0.0231</t>
-  </si>
-  <si>
-    <t>0.8109,0.0627,0.0561,0.0098</t>
-  </si>
-  <si>
-    <t>0.7813,0.0903,0.0952,0.0059</t>
-  </si>
-  <si>
-    <t>0.7624,0.2033,0.0498,0.0015</t>
-  </si>
-  <si>
-    <t>0.7267,0.2289,0.0653,0.0024</t>
-  </si>
-  <si>
-    <t>0.8755,0.0488,0.0362,0.0030</t>
-  </si>
-  <si>
-    <t>0.6016,0.2166,0.0611,0.0224</t>
-  </si>
-  <si>
-    <t>0.6514,0.2554,0.0872,0.0093</t>
-  </si>
-  <si>
-    <t>0.7878,0.1150,0.0671,0.0059</t>
-  </si>
-  <si>
-    <t>0.7909,0.0448,0.0402,0.0205</t>
-  </si>
-  <si>
-    <t>0.1141,0.0618,0.9323,0.0005</t>
-  </si>
-  <si>
-    <t>0.6499,0.2053,0.0808,0.0154</t>
-  </si>
-  <si>
-    <t>0.6672,0.0152,0.3401,0.0003</t>
-  </si>
-  <si>
-    <t>0.9576,0.0030,0.0540,0.0001</t>
-  </si>
-  <si>
-    <t>0.9006,0.0112,0.1032,0.0003</t>
-  </si>
-  <si>
-    <t>0.5562,0.0425,0.3890,0.0004</t>
-  </si>
-  <si>
-    <t>0.8639,0.0395,0.0970,0.0004</t>
-  </si>
-  <si>
-    <t>0.7250,0.0070,0.3993,0.0008</t>
-  </si>
-  <si>
-    <t>0.8432,0.0056,0.2732,0.0001</t>
-  </si>
-  <si>
-    <t>0.9132,0.0243,0.0535,0.0005</t>
-  </si>
-  <si>
-    <t>0.9173,0.0469,0.0268,0.0006</t>
-  </si>
-  <si>
-    <t>0.8959,0.0279,0.0485,0.0014</t>
-  </si>
-  <si>
-    <t>0.9220,0.0231,0.0478,0.0005</t>
-  </si>
-  <si>
-    <t>0.8583,0.0511,0.1041,0.0005</t>
-  </si>
-  <si>
-    <t>0.9143,0.0321,0.0462,0.0010</t>
-  </si>
-  <si>
-    <t>0.9128,0.0234,0.0498,0.0014</t>
-  </si>
-  <si>
-    <t>0.9433,0.0095,0.0422,0.0002</t>
-  </si>
-  <si>
-    <t>0.7591,0.1056,0.0668,0.0134</t>
-  </si>
-  <si>
-    <t>0.8137,0.0887,0.0346,0.0053</t>
-  </si>
-  <si>
-    <t>0.7969,0.1256,0.0471,0.0047</t>
-  </si>
-  <si>
-    <t>0.7381,0.0932,0.0566,0.0181</t>
-  </si>
-  <si>
-    <t>0.7577,0.0641,0.0423,0.0201</t>
-  </si>
-  <si>
-    <t>0.9563,0.0120,0.0220,0.0002</t>
-  </si>
-  <si>
-    <t>0.8327,0.0428,0.1446,0.0019</t>
-  </si>
-  <si>
-    <t>0.9632,0.0119,0.0153,0.0003</t>
-  </si>
-  <si>
-    <t>0.9272,0.0073,0.0786,0.0002</t>
-  </si>
-  <si>
-    <t>0.9278,0.0223,0.0372,0.0004</t>
-  </si>
-  <si>
-    <t>0.7074,0.0962,0.2667,0.0026</t>
-  </si>
-  <si>
-    <t>0.9182,0.0065,0.0974,0.0001</t>
-  </si>
-  <si>
-    <t>0.9595,0.0017,0.0491,0.0001</t>
-  </si>
-  <si>
-    <t>0.9696,0.0017,0.0213,0.0000</t>
-  </si>
-  <si>
-    <t>0.9508,0.0037,0.0354,0.0001</t>
-  </si>
-  <si>
-    <t>0.6965,0.1195,0.0316,0.0146</t>
-  </si>
-  <si>
-    <t>0.6953,0.1638,0.0501,0.0101</t>
-  </si>
-  <si>
-    <t>0.8593,0.0506,0.0384,0.0063</t>
-  </si>
-  <si>
-    <t>0.9041,0.0316,0.0161,0.0055</t>
-  </si>
-  <si>
-    <t>0.7668,0.0828,0.0532,0.0224</t>
-  </si>
-  <si>
-    <t>0.8719,0.0351,0.0285,0.0094</t>
-  </si>
-  <si>
-    <t>0.7983,0.0714,0.0239,0.0124</t>
-  </si>
-  <si>
-    <t>0.8689,0.0560,0.0325,0.0040</t>
-  </si>
-  <si>
-    <t>0.9031,0.0324,0.0662,0.0005</t>
-  </si>
-  <si>
-    <t>0.9379,0.0213,0.0262,0.0010</t>
-  </si>
-  <si>
-    <t>0.7805,0.0772,0.1201,0.0048</t>
-  </si>
-  <si>
-    <t>0.8725,0.0019,0.2236,0.0001</t>
-  </si>
-  <si>
-    <t>0.4587,0.0124,0.7077,0.0007</t>
-  </si>
-  <si>
-    <t>0.6759,0.0501,0.2259,0.0004</t>
-  </si>
-  <si>
-    <t>0.8169,0.0022,0.3357,0.0000</t>
-  </si>
-  <si>
-    <t>0.8000,0.0299,0.1599,0.0006</t>
-  </si>
-  <si>
-    <t>0.5156,0.0036,0.7467,0.0002</t>
-  </si>
-  <si>
-    <t>0.9604,0.0024,0.0256,0.0003</t>
-  </si>
-  <si>
-    <t>0.9238,0.0063,0.0990,0.0005</t>
-  </si>
-  <si>
-    <t>0.9491,0.0102,0.0275,0.0006</t>
-  </si>
-  <si>
-    <t>0.9622,0.0048,0.0321,0.0001</t>
-  </si>
-  <si>
-    <t>0.8797,0.0209,0.1050,0.0006</t>
-  </si>
-  <si>
-    <t>0.6348,0.1354,0.0767,0.0322</t>
-  </si>
-  <si>
-    <t>0.6440,0.1932,0.0956,0.0225</t>
-  </si>
-  <si>
-    <t>0.6501,0.1667,0.0999,0.0275</t>
-  </si>
-  <si>
-    <t>0.5595,0.2944,0.0889,0.0150</t>
-  </si>
-  <si>
-    <t>0.8131,0.0523,0.0327,0.0160</t>
-  </si>
-  <si>
-    <t>0.8185,0.0538,0.0287,0.0179</t>
-  </si>
-  <si>
-    <t>0.7506,0.1127,0.0922,0.0102</t>
-  </si>
-  <si>
-    <t>0.6314,0.0862,0.0353,0.0427</t>
-  </si>
-  <si>
-    <t>0.8499,0.0177,0.1832,0.0002</t>
-  </si>
-  <si>
-    <t>0.6231,0.0183,0.4730,0.0002</t>
-  </si>
-  <si>
-    <t>0.5642,0.0182,0.5233,0.0001</t>
-  </si>
-  <si>
-    <t>0.9554,0.0090,0.0249,0.0003</t>
-  </si>
-  <si>
-    <t>0.8357,0.0051,0.2647,0.0004</t>
-  </si>
-  <si>
-    <t>0.9642,0.0037,0.0266,0.0002</t>
-  </si>
-  <si>
-    <t>0.9401,0.0117,0.0331,0.0003</t>
-  </si>
-  <si>
-    <t>0.9269,0.0146,0.0555,0.0008</t>
-  </si>
-  <si>
-    <t>0.8734,0.0701,0.0420,0.0015</t>
-  </si>
-  <si>
-    <t>0.9507,0.0084,0.0167,0.0010</t>
-  </si>
-  <si>
-    <t>0.9067,0.0219,0.0328,0.0037</t>
-  </si>
-  <si>
-    <t>0.8741,0.0362,0.0253,0.0070</t>
-  </si>
-  <si>
-    <t>0.9231,0.0221,0.0145,0.0032</t>
-  </si>
-  <si>
-    <t>0.8754,0.0782,0.0336,0.0008</t>
+    <t>0.8558,0.0581,0.0601,0.0043</t>
+  </si>
+  <si>
+    <t>0.9167,0.0392,0.0154,0.0024</t>
+  </si>
+  <si>
+    <t>0.7893,0.0640,0.0752,0.0102</t>
+  </si>
+  <si>
+    <t>0.9205,0.0246,0.0159,0.0031</t>
+  </si>
+  <si>
+    <t>0.8234,0.0432,0.0416,0.0171</t>
+  </si>
+  <si>
+    <t>0.5515,0.1281,0.0565,0.0542</t>
+  </si>
+  <si>
+    <t>0.8313,0.0691,0.0208,0.0082</t>
+  </si>
+  <si>
+    <t>0.7385,0.1164,0.1039,0.0113</t>
+  </si>
+  <si>
+    <t>0.8514,0.0379,0.0395,0.0082</t>
+  </si>
+  <si>
+    <t>0.7725,0.1094,0.0471,0.0166</t>
+  </si>
+  <si>
+    <t>0.7278,0.1016,0.0540,0.0167</t>
+  </si>
+  <si>
+    <t>0.6858,0.0757,0.0341,0.0409</t>
+  </si>
+  <si>
+    <t>0.9836,0.0038,0.0058,0.0001</t>
+  </si>
+  <si>
+    <t>0.9115,0.0280,0.0541,0.0004</t>
+  </si>
+  <si>
+    <t>0.9244,0.0121,0.0597,0.0004</t>
+  </si>
+  <si>
+    <t>0.7748,0.0065,0.3975,0.0001</t>
+  </si>
+  <si>
+    <t>0.9047,0.0460,0.0498,0.0006</t>
+  </si>
+  <si>
+    <t>0.5443,0.5544,0.0658,0.0011</t>
+  </si>
+  <si>
+    <t>0.5225,0.4020,0.1112,0.0079</t>
+  </si>
+  <si>
+    <t>0.7968,0.0900,0.0924,0.0045</t>
+  </si>
+  <si>
+    <t>0.2355,0.7797,0.1716,0.0032</t>
+  </si>
+  <si>
+    <t>0.0676,0.9430,0.0935,0.0007</t>
+  </si>
+  <si>
+    <t>0.9530,0.0079,0.0225,0.0006</t>
+  </si>
+  <si>
+    <t>0.9791,0.0018,0.0113,0.0000</t>
+  </si>
+  <si>
+    <t>0.9574,0.0024,0.0338,0.0002</t>
+  </si>
+  <si>
+    <t>0.9417,0.0086,0.0497,0.0001</t>
+  </si>
+  <si>
+    <t>0.9685,0.0019,0.0308,0.0000</t>
+  </si>
+  <si>
+    <t>0.9188,0.0113,0.0816,0.0003</t>
+  </si>
+  <si>
+    <t>0.8694,0.0040,0.1807,0.0002</t>
+  </si>
+  <si>
+    <t>0.9049,0.0705,0.0296,0.0002</t>
+  </si>
+  <si>
+    <t>0.8214,0.0832,0.1072,0.0013</t>
+  </si>
+  <si>
+    <t>0.1228,0.4528,0.7854,0.0074</t>
+  </si>
+  <si>
+    <t>0.7315,0.2283,0.0847,0.0013</t>
+  </si>
+  <si>
+    <t>0.7485,0.2355,0.0539,0.0023</t>
+  </si>
+  <si>
+    <t>0.7832,0.1812,0.0735,0.0031</t>
+  </si>
+  <si>
+    <t>0.8065,0.1275,0.0485,0.0039</t>
+  </si>
+  <si>
+    <t>0.8044,0.1371,0.0598,0.0021</t>
+  </si>
+  <si>
+    <t>0.7026,0.1748,0.0372,0.0004</t>
+  </si>
+  <si>
+    <t>0.9558,0.0027,0.0306,0.0003</t>
+  </si>
+  <si>
+    <t>0.9824,0.0011,0.0179,0.0000</t>
+  </si>
+  <si>
+    <t>0.9848,0.0007,0.0096,0.0000</t>
+  </si>
+  <si>
+    <t>0.9798,0.0008,0.0256,0.0001</t>
+  </si>
+  <si>
+    <t>0.3752,0.6253,0.0613,0.0007</t>
+  </si>
+  <si>
+    <t>0.9663,0.0044,0.0286,0.0002</t>
+  </si>
+  <si>
+    <t>0.9037,0.0856,0.0119,0.0008</t>
+  </si>
+  <si>
+    <t>0.7193,0.4002,0.0232,0.0003</t>
+  </si>
+  <si>
+    <t>0.2835,0.8087,0.0568,0.0002</t>
+  </si>
+  <si>
+    <t>0.0948,0.9367,0.0627,0.0005</t>
+  </si>
+  <si>
+    <t>0.6932,0.0068,0.4025,0.0002</t>
+  </si>
+  <si>
+    <t>0.4056,0.0346,0.7004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9575,0.0022,0.0461,0.0001</t>
+  </si>
+  <si>
+    <t>0.7393,0.0121,0.3604,0.0003</t>
+  </si>
+  <si>
+    <t>0.3352,0.0381,0.7614,0.0008</t>
+  </si>
+  <si>
+    <t>0.7637,0.0115,0.2797,0.0001</t>
+  </si>
+  <si>
+    <t>0.8325,0.0841,0.0374,0.0058</t>
+  </si>
+  <si>
+    <t>0.7306,0.0947,0.1327,0.0112</t>
+  </si>
+  <si>
+    <t>0.6781,0.1651,0.0432,0.0176</t>
+  </si>
+  <si>
+    <t>0.1837,0.1531,0.8550,0.0017</t>
+  </si>
+  <si>
+    <t>0.8231,0.0557,0.0274,0.0110</t>
+  </si>
+  <si>
+    <t>0.7951,0.0603,0.0397,0.0157</t>
+  </si>
+  <si>
+    <t>0.7066,0.1491,0.0868,0.0133</t>
+  </si>
+  <si>
+    <t>0.7660,0.0300,0.1801,0.0002</t>
+  </si>
+  <si>
+    <t>0.7533,0.0140,0.3257,0.0003</t>
+  </si>
+  <si>
+    <t>0.7251,0.0147,0.3556,0.0007</t>
+  </si>
+  <si>
+    <t>0.6763,0.1042,0.1813,0.0002</t>
+  </si>
+  <si>
+    <t>0.5278,0.0056,0.7186,0.0002</t>
+  </si>
+  <si>
+    <t>0.8616,0.1278,0.0205,0.0009</t>
+  </si>
+  <si>
+    <t>0.0090,0.9914,0.0254,0.0001</t>
+  </si>
+  <si>
+    <t>0.9192,0.0247,0.0143,0.0037</t>
+  </si>
+  <si>
+    <t>0.9177,0.0299,0.0459,0.0005</t>
+  </si>
+  <si>
+    <t>0.3239,0.1486,0.7094,0.0014</t>
+  </si>
+  <si>
+    <t>0.6784,0.0605,0.2516,0.0004</t>
+  </si>
+  <si>
+    <t>0.9096,0.0126,0.0735,0.0000</t>
+  </si>
+  <si>
+    <t>0.3204,0.6785,0.0334,0.0000</t>
+  </si>
+  <si>
+    <t>0.4750,0.3427,0.0914,0.0001</t>
+  </si>
+  <si>
+    <t>0.9476,0.0255,0.0143,0.0006</t>
+  </si>
+  <si>
+    <t>0.8152,0.0361,0.0312,0.0232</t>
+  </si>
+  <si>
+    <t>0.9414,0.0315,0.0131,0.0019</t>
+  </si>
+  <si>
+    <t>0.9505,0.0153,0.0110,0.0029</t>
+  </si>
+  <si>
+    <t>0.9333,0.0125,0.0150,0.0041</t>
+  </si>
+  <si>
+    <t>0.9610,0.0159,0.0092,0.0006</t>
+  </si>
+  <si>
+    <t>0.7650,0.0969,0.1300,0.0002</t>
+  </si>
+  <si>
+    <t>0.8999,0.0067,0.1120,0.0004</t>
+  </si>
+  <si>
+    <t>0.5070,0.0489,0.5462,0.0005</t>
+  </si>
+  <si>
+    <t>0.8047,0.0094,0.2780,0.0002</t>
+  </si>
+  <si>
+    <t>0.5390,0.0427,0.4817,0.0002</t>
+  </si>
+  <si>
+    <t>0.6380,0.0703,0.2399,0.0003</t>
+  </si>
+  <si>
+    <t>0.8305,0.0639,0.0660,0.0064</t>
+  </si>
+  <si>
+    <t>0.8322,0.0764,0.0243,0.0066</t>
+  </si>
+  <si>
+    <t>0.7285,0.1358,0.0453,0.0162</t>
+  </si>
+  <si>
+    <t>0.8722,0.0621,0.0263,0.0063</t>
+  </si>
+  <si>
+    <t>0.7219,0.1112,0.0597,0.0119</t>
+  </si>
+  <si>
+    <t>0.8707,0.0197,0.0212,0.0171</t>
+  </si>
+  <si>
+    <t>0.7531,0.0535,0.0414,0.0312</t>
+  </si>
+  <si>
+    <t>0.7661,0.0968,0.0548,0.0148</t>
+  </si>
+  <si>
+    <t>0.7436,0.0668,0.0828,0.0251</t>
+  </si>
+  <si>
+    <t>0.6947,0.1123,0.0773,0.0252</t>
+  </si>
+  <si>
+    <t>0.7460,0.0471,0.0376,0.0375</t>
+  </si>
+  <si>
+    <t>0.8211,0.0767,0.0254,0.0072</t>
+  </si>
+  <si>
+    <t>0.7853,0.0282,0.0223,0.0367</t>
+  </si>
+  <si>
+    <t>0.8623,0.0250,0.0180,0.0131</t>
+  </si>
+  <si>
+    <t>0.7972,0.0666,0.0547,0.0112</t>
+  </si>
+  <si>
+    <t>0.7565,0.0293,0.0351,0.0455</t>
+  </si>
+  <si>
+    <t>0.1083,0.0146,0.9624,0.0001</t>
+  </si>
+  <si>
+    <t>0.9615,0.0052,0.0281,0.0001</t>
+  </si>
+  <si>
+    <t>0.9591,0.0080,0.0206,0.0004</t>
+  </si>
+  <si>
+    <t>0.9655,0.0010,0.0221,0.0004</t>
+  </si>
+  <si>
+    <t>0.5152,0.5248,0.0767,0.0032</t>
+  </si>
+  <si>
+    <t>0.8119,0.1726,0.0396,0.0013</t>
+  </si>
+  <si>
+    <t>0.6579,0.2604,0.0892,0.0042</t>
+  </si>
+  <si>
+    <t>0.4746,0.4264,0.1757,0.0040</t>
+  </si>
+  <si>
+    <t>0.6104,0.4485,0.0548,0.0023</t>
+  </si>
+  <si>
+    <t>0.8448,0.1639,0.0349,0.0010</t>
+  </si>
+  <si>
+    <t>0.7484,0.1829,0.0785,0.0026</t>
+  </si>
+  <si>
+    <t>0.8656,0.0795,0.0439,0.0010</t>
+  </si>
+  <si>
+    <t>0.9094,0.0146,0.0857,0.0003</t>
+  </si>
+  <si>
+    <t>0.9298,0.0149,0.0462,0.0007</t>
+  </si>
+  <si>
+    <t>0.8350,0.0709,0.0878,0.0017</t>
+  </si>
+  <si>
+    <t>0.9482,0.0160,0.0187,0.0008</t>
+  </si>
+  <si>
+    <t>0.3255,0.7316,0.1045,0.0009</t>
+  </si>
+  <si>
+    <t>0.4248,0.6925,0.0375,0.0006</t>
+  </si>
+  <si>
+    <t>0.8503,0.1416,0.0267,0.0009</t>
+  </si>
+  <si>
+    <t>0.1403,0.8354,0.2799,0.0014</t>
+  </si>
+  <si>
+    <t>0.8722,0.0620,0.0462,0.0007</t>
+  </si>
+  <si>
+    <t>0.7943,0.0956,0.0615,0.0058</t>
+  </si>
+  <si>
+    <t>0.8201,0.1032,0.0660,0.0028</t>
+  </si>
+  <si>
+    <t>0.8399,0.0640,0.0428,0.0057</t>
+  </si>
+  <si>
+    <t>0.7862,0.0576,0.0306,0.0216</t>
+  </si>
+  <si>
+    <t>0.8435,0.0482,0.0214,0.0111</t>
+  </si>
+  <si>
+    <t>0.8678,0.0721,0.0330,0.0024</t>
+  </si>
+  <si>
+    <t>0.8281,0.0309,0.0202,0.0268</t>
+  </si>
+  <si>
+    <t>0.7445,0.1644,0.0549,0.0076</t>
+  </si>
+  <si>
+    <t>0.7870,0.0331,0.0255,0.0445</t>
+  </si>
+  <si>
+    <t>0.7302,0.1563,0.0735,0.0110</t>
+  </si>
+  <si>
+    <t>0.9490,0.0116,0.0232,0.0001</t>
+  </si>
+  <si>
+    <t>0.8878,0.0024,0.1675,0.0001</t>
+  </si>
+  <si>
+    <t>0.5363,0.0291,0.5266,0.0003</t>
+  </si>
+  <si>
+    <t>0.8937,0.0202,0.1119,0.0008</t>
+  </si>
+  <si>
+    <t>0.9114,0.0364,0.0401,0.0004</t>
+  </si>
+  <si>
+    <t>0.8836,0.0723,0.0367,0.0003</t>
+  </si>
+  <si>
+    <t>0.9391,0.0090,0.0435,0.0005</t>
+  </si>
+  <si>
+    <t>0.9012,0.0297,0.0580,0.0008</t>
+  </si>
+  <si>
+    <t>0.9643,0.0117,0.0100,0.0005</t>
+  </si>
+  <si>
+    <t>0.8870,0.0163,0.0209,0.0143</t>
+  </si>
+  <si>
+    <t>0.9314,0.0206,0.0259,0.0014</t>
+  </si>
+  <si>
+    <t>0.9060,0.0096,0.0180,0.0094</t>
+  </si>
+  <si>
+    <t>0.8313,0.0257,0.1824,0.0010</t>
+  </si>
+  <si>
+    <t>0.7996,0.1552,0.0472,0.0027</t>
+  </si>
+  <si>
+    <t>0.7626,0.0977,0.0576,0.0164</t>
+  </si>
+  <si>
+    <t>0.8110,0.0606,0.0362,0.0131</t>
+  </si>
+  <si>
+    <t>0.7844,0.0444,0.0395,0.0215</t>
+  </si>
+  <si>
+    <t>0.7328,0.1960,0.0771,0.0046</t>
+  </si>
+  <si>
+    <t>0.9035,0.0454,0.0236,0.0019</t>
+  </si>
+  <si>
+    <t>0.5714,0.1280,0.0295,0.0335</t>
+  </si>
+  <si>
+    <t>0.3257,0.1176,0.6949,0.0087</t>
+  </si>
+  <si>
+    <t>0.8982,0.0278,0.0278,0.0060</t>
+  </si>
+  <si>
+    <t>0.8369,0.0801,0.0462,0.0042</t>
+  </si>
+  <si>
+    <t>0.6611,0.3156,0.0969,0.0016</t>
+  </si>
+  <si>
+    <t>0.8982,0.0510,0.0341,0.0008</t>
+  </si>
+  <si>
+    <t>0.9012,0.0535,0.0252,0.0011</t>
+  </si>
+  <si>
+    <t>0.6638,0.3459,0.0688,0.0047</t>
+  </si>
+  <si>
+    <t>0.8170,0.1526,0.0515,0.0009</t>
+  </si>
+  <si>
+    <t>0.8686,0.0706,0.0704,0.0016</t>
+  </si>
+  <si>
+    <t>0.6828,0.1462,0.0736,0.0166</t>
+  </si>
+  <si>
+    <t>0.7957,0.0721,0.0452,0.0150</t>
+  </si>
+  <si>
+    <t>0.8035,0.1011,0.0371,0.0071</t>
+  </si>
+  <si>
+    <t>0.8596,0.0378,0.0290,0.0088</t>
+  </si>
+  <si>
+    <t>0.7340,0.1866,0.0856,0.0042</t>
+  </si>
+  <si>
+    <t>0.6136,0.1291,0.0598,0.0358</t>
+  </si>
+  <si>
+    <t>0.7019,0.1317,0.0254,0.0134</t>
+  </si>
+  <si>
+    <t>0.8239,0.0316,0.0304,0.0278</t>
+  </si>
+  <si>
+    <t>0.7943,0.0820,0.0883,0.0062</t>
+  </si>
+  <si>
+    <t>0.8278,0.1148,0.0376,0.0033</t>
+  </si>
+  <si>
+    <t>0.6996,0.2167,0.0838,0.0031</t>
+  </si>
+  <si>
+    <t>0.7843,0.0886,0.0294,0.0056</t>
+  </si>
+  <si>
+    <t>0.7586,0.0926,0.0683,0.0140</t>
+  </si>
+  <si>
+    <t>0.8624,0.0346,0.0323,0.0086</t>
+  </si>
+  <si>
+    <t>0.6756,0.1467,0.1261,0.0287</t>
+  </si>
+  <si>
+    <t>0.6872,0.0990,0.1018,0.0296</t>
+  </si>
+  <si>
+    <t>0.4314,0.0297,0.7475,0.0009</t>
+  </si>
+  <si>
+    <t>0.5736,0.3140,0.0780,0.0142</t>
+  </si>
+  <si>
+    <t>0.7762,0.0195,0.2616,0.0005</t>
+  </si>
+  <si>
+    <t>0.9541,0.0036,0.0494,0.0002</t>
+  </si>
+  <si>
+    <t>0.9167,0.0130,0.0765,0.0002</t>
+  </si>
+  <si>
+    <t>0.8107,0.0226,0.1527,0.0006</t>
+  </si>
+  <si>
+    <t>0.9325,0.0070,0.0685,0.0001</t>
+  </si>
+  <si>
+    <t>0.9309,0.0025,0.0859,0.0001</t>
+  </si>
+  <si>
+    <t>0.5886,0.0147,0.6036,0.0003</t>
+  </si>
+  <si>
+    <t>0.8888,0.0198,0.1084,0.0005</t>
+  </si>
+  <si>
+    <t>0.9225,0.0226,0.0438,0.0007</t>
+  </si>
+  <si>
+    <t>0.6538,0.1932,0.1232,0.0002</t>
+  </si>
+  <si>
+    <t>0.7696,0.1314,0.1287,0.0011</t>
+  </si>
+  <si>
+    <t>0.9535,0.0167,0.0214,0.0002</t>
+  </si>
+  <si>
+    <t>0.9660,0.0096,0.0134,0.0002</t>
+  </si>
+  <si>
+    <t>0.9585,0.0097,0.0167,0.0004</t>
+  </si>
+  <si>
+    <t>0.9288,0.0319,0.0232,0.0007</t>
+  </si>
+  <si>
+    <t>0.7133,0.1251,0.0411,0.0146</t>
+  </si>
+  <si>
+    <t>0.6781,0.2092,0.0684,0.0109</t>
+  </si>
+  <si>
+    <t>0.8094,0.0796,0.0747,0.0071</t>
+  </si>
+  <si>
+    <t>0.5962,0.1551,0.0609,0.0315</t>
+  </si>
+  <si>
+    <t>0.4417,0.0875,0.0517,0.1594</t>
+  </si>
+  <si>
+    <t>0.9563,0.0140,0.0181,0.0002</t>
+  </si>
+  <si>
+    <t>0.9617,0.0086,0.0250,0.0001</t>
+  </si>
+  <si>
+    <t>0.9847,0.0035,0.0062,0.0002</t>
+  </si>
+  <si>
+    <t>0.9483,0.0069,0.0478,0.0001</t>
+  </si>
+  <si>
+    <t>0.9552,0.0094,0.0346,0.0002</t>
+  </si>
+  <si>
+    <t>0.8656,0.0394,0.0838,0.0016</t>
+  </si>
+  <si>
+    <t>0.9421,0.0047,0.0625,0.0003</t>
+  </si>
+  <si>
+    <t>0.9894,0.0007,0.0060,0.0001</t>
+  </si>
+  <si>
+    <t>0.9258,0.0020,0.0497,0.0005</t>
+  </si>
+  <si>
+    <t>0.8258,0.0171,0.1638,0.0002</t>
+  </si>
+  <si>
+    <t>0.7459,0.0833,0.0382,0.0161</t>
+  </si>
+  <si>
+    <t>0.8073,0.0599,0.0400,0.0144</t>
+  </si>
+  <si>
+    <t>0.7422,0.1620,0.0704,0.0063</t>
+  </si>
+  <si>
+    <t>0.7193,0.1088,0.1012,0.0162</t>
+  </si>
+  <si>
+    <t>0.6990,0.0644,0.0536,0.0370</t>
+  </si>
+  <si>
+    <t>0.8440,0.0540,0.0279,0.0097</t>
+  </si>
+  <si>
+    <t>0.7987,0.0412,0.0210,0.0226</t>
+  </si>
+  <si>
+    <t>0.8483,0.0465,0.0277,0.0095</t>
+  </si>
+  <si>
+    <t>0.8057,0.0528,0.1469,0.0016</t>
+  </si>
+  <si>
+    <t>0.8799,0.0426,0.0665,0.0018</t>
+  </si>
+  <si>
+    <t>0.8623,0.0810,0.0383,0.0030</t>
+  </si>
+  <si>
+    <t>0.9468,0.0010,0.0805,0.0002</t>
+  </si>
+  <si>
+    <t>0.7606,0.0050,0.3179,0.0013</t>
+  </si>
+  <si>
+    <t>0.9719,0.0063,0.0182,0.0001</t>
+  </si>
+  <si>
+    <t>0.8991,0.0017,0.1600,0.0002</t>
+  </si>
+  <si>
+    <t>0.9780,0.0011,0.0246,0.0000</t>
+  </si>
+  <si>
+    <t>0.5253,0.0033,0.7117,0.0004</t>
+  </si>
+  <si>
+    <t>0.8966,0.0053,0.1244,0.0002</t>
+  </si>
+  <si>
+    <t>0.9354,0.0053,0.0751,0.0001</t>
+  </si>
+  <si>
+    <t>0.8982,0.0155,0.1108,0.0006</t>
+  </si>
+  <si>
+    <t>0.9697,0.0057,0.0181,0.0002</t>
+  </si>
+  <si>
+    <t>0.9183,0.0141,0.0539,0.0015</t>
+  </si>
+  <si>
+    <t>0.7613,0.0803,0.0432,0.0191</t>
+  </si>
+  <si>
+    <t>0.8564,0.0829,0.0209,0.0033</t>
+  </si>
+  <si>
+    <t>0.8819,0.0278,0.0265,0.0090</t>
+  </si>
+  <si>
+    <t>0.7926,0.0670,0.0683,0.0072</t>
+  </si>
+  <si>
+    <t>0.7569,0.0510,0.0403,0.0295</t>
+  </si>
+  <si>
+    <t>0.6715,0.0893,0.0291,0.0369</t>
+  </si>
+  <si>
+    <t>0.6919,0.1145,0.0732,0.0366</t>
+  </si>
+  <si>
+    <t>0.7513,0.1030,0.0416,0.0101</t>
+  </si>
+  <si>
+    <t>0.9653,0.0045,0.0222,0.0001</t>
+  </si>
+  <si>
+    <t>0.7679,0.0271,0.1806,0.0002</t>
+  </si>
+  <si>
+    <t>0.8415,0.0071,0.1755,0.0001</t>
+  </si>
+  <si>
+    <t>0.9370,0.0144,0.0505,0.0003</t>
+  </si>
+  <si>
+    <t>0.8823,0.0045,0.1781,0.0003</t>
+  </si>
+  <si>
+    <t>0.9724,0.0023,0.0143,0.0004</t>
+  </si>
+  <si>
+    <t>0.8473,0.0164,0.2039,0.0005</t>
+  </si>
+  <si>
+    <t>0.9558,0.0051,0.0207,0.0006</t>
+  </si>
+  <si>
+    <t>0.8586,0.0375,0.0395,0.0063</t>
+  </si>
+  <si>
+    <t>0.9246,0.0172,0.0172,0.0035</t>
+  </si>
+  <si>
+    <t>0.9676,0.0126,0.0054,0.0005</t>
+  </si>
+  <si>
+    <t>0.9095,0.0183,0.0308,0.0047</t>
+  </si>
+  <si>
+    <t>0.8744,0.0210,0.0244,0.0119</t>
+  </si>
+  <si>
+    <t>0.9023,0.0322,0.0504,0.0013</t>
   </si>
 </sst>
 </file>
@@ -2191,7 +2191,7 @@
         <v>262</v>
       </c>
       <c r="C19" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D19" t="s">
         <v>281</v>
@@ -2205,7 +2205,7 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D20" t="s">
         <v>282</v>
@@ -2345,7 +2345,7 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D30" t="s">
         <v>292</v>
@@ -2541,7 +2541,7 @@
         <v>262</v>
       </c>
       <c r="C44" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>306</v>
@@ -2681,7 +2681,7 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D54" t="s">
         <v>316</v>
@@ -2933,7 +2933,7 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
         <v>334</v>
@@ -2975,7 +2975,7 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
         <v>337</v>
@@ -3115,7 +3115,7 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
         <v>347</v>
@@ -3395,7 +3395,7 @@
         <v>261</v>
       </c>
       <c r="C105" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D105" t="s">
         <v>367</v>
@@ -3465,7 +3465,7 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D110" t="s">
         <v>372</v>
@@ -3507,7 +3507,7 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D113" t="s">
         <v>375</v>
@@ -3521,7 +3521,7 @@
         <v>262</v>
       </c>
       <c r="C114" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D114" t="s">
         <v>376</v>
@@ -3857,7 +3857,7 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
         <v>400</v>
@@ -4571,7 +4571,7 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
         <v>451</v>
@@ -5075,7 +5075,7 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D225" t="s">
         <v>487</v>
@@ -5355,7 +5355,7 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D245" t="s">
         <v>507</v>

--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_100/per_file_predictions_epoch_100.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_1/epoch_100/per_file_predictions_epoch_100.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,772 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8558,0.0581,0.0601,0.0043</t>
-  </si>
-  <si>
-    <t>0.9167,0.0392,0.0154,0.0024</t>
-  </si>
-  <si>
-    <t>0.7893,0.0640,0.0752,0.0102</t>
-  </si>
-  <si>
-    <t>0.9205,0.0246,0.0159,0.0031</t>
-  </si>
-  <si>
-    <t>0.8234,0.0432,0.0416,0.0171</t>
-  </si>
-  <si>
-    <t>0.5515,0.1281,0.0565,0.0542</t>
-  </si>
-  <si>
-    <t>0.8313,0.0691,0.0208,0.0082</t>
-  </si>
-  <si>
-    <t>0.7385,0.1164,0.1039,0.0113</t>
-  </si>
-  <si>
-    <t>0.8514,0.0379,0.0395,0.0082</t>
-  </si>
-  <si>
-    <t>0.7725,0.1094,0.0471,0.0166</t>
-  </si>
-  <si>
-    <t>0.7278,0.1016,0.0540,0.0167</t>
-  </si>
-  <si>
-    <t>0.6858,0.0757,0.0341,0.0409</t>
-  </si>
-  <si>
-    <t>0.9836,0.0038,0.0058,0.0001</t>
-  </si>
-  <si>
-    <t>0.9115,0.0280,0.0541,0.0004</t>
-  </si>
-  <si>
-    <t>0.9244,0.0121,0.0597,0.0004</t>
-  </si>
-  <si>
-    <t>0.7748,0.0065,0.3975,0.0001</t>
-  </si>
-  <si>
-    <t>0.9047,0.0460,0.0498,0.0006</t>
-  </si>
-  <si>
-    <t>0.5443,0.5544,0.0658,0.0011</t>
-  </si>
-  <si>
-    <t>0.5225,0.4020,0.1112,0.0079</t>
-  </si>
-  <si>
-    <t>0.7968,0.0900,0.0924,0.0045</t>
-  </si>
-  <si>
-    <t>0.2355,0.7797,0.1716,0.0032</t>
-  </si>
-  <si>
-    <t>0.0676,0.9430,0.0935,0.0007</t>
-  </si>
-  <si>
-    <t>0.9530,0.0079,0.0225,0.0006</t>
-  </si>
-  <si>
-    <t>0.9791,0.0018,0.0113,0.0000</t>
-  </si>
-  <si>
-    <t>0.9574,0.0024,0.0338,0.0002</t>
-  </si>
-  <si>
-    <t>0.9417,0.0086,0.0497,0.0001</t>
-  </si>
-  <si>
-    <t>0.9685,0.0019,0.0308,0.0000</t>
-  </si>
-  <si>
-    <t>0.9188,0.0113,0.0816,0.0003</t>
-  </si>
-  <si>
-    <t>0.8694,0.0040,0.1807,0.0002</t>
-  </si>
-  <si>
-    <t>0.9049,0.0705,0.0296,0.0002</t>
-  </si>
-  <si>
-    <t>0.8214,0.0832,0.1072,0.0013</t>
-  </si>
-  <si>
-    <t>0.1228,0.4528,0.7854,0.0074</t>
-  </si>
-  <si>
-    <t>0.7315,0.2283,0.0847,0.0013</t>
-  </si>
-  <si>
-    <t>0.7485,0.2355,0.0539,0.0023</t>
-  </si>
-  <si>
-    <t>0.7832,0.1812,0.0735,0.0031</t>
-  </si>
-  <si>
-    <t>0.8065,0.1275,0.0485,0.0039</t>
-  </si>
-  <si>
-    <t>0.8044,0.1371,0.0598,0.0021</t>
-  </si>
-  <si>
-    <t>0.7026,0.1748,0.0372,0.0004</t>
-  </si>
-  <si>
-    <t>0.9558,0.0027,0.0306,0.0003</t>
-  </si>
-  <si>
-    <t>0.9824,0.0011,0.0179,0.0000</t>
-  </si>
-  <si>
-    <t>0.9848,0.0007,0.0096,0.0000</t>
-  </si>
-  <si>
-    <t>0.9798,0.0008,0.0256,0.0001</t>
-  </si>
-  <si>
-    <t>0.3752,0.6253,0.0613,0.0007</t>
-  </si>
-  <si>
-    <t>0.9663,0.0044,0.0286,0.0002</t>
-  </si>
-  <si>
-    <t>0.9037,0.0856,0.0119,0.0008</t>
-  </si>
-  <si>
-    <t>0.7193,0.4002,0.0232,0.0003</t>
-  </si>
-  <si>
-    <t>0.2835,0.8087,0.0568,0.0002</t>
-  </si>
-  <si>
-    <t>0.0948,0.9367,0.0627,0.0005</t>
-  </si>
-  <si>
-    <t>0.6932,0.0068,0.4025,0.0002</t>
-  </si>
-  <si>
-    <t>0.4056,0.0346,0.7004,0.0006</t>
-  </si>
-  <si>
-    <t>0.9575,0.0022,0.0461,0.0001</t>
-  </si>
-  <si>
-    <t>0.7393,0.0121,0.3604,0.0003</t>
-  </si>
-  <si>
-    <t>0.3352,0.0381,0.7614,0.0008</t>
-  </si>
-  <si>
-    <t>0.7637,0.0115,0.2797,0.0001</t>
-  </si>
-  <si>
-    <t>0.8325,0.0841,0.0374,0.0058</t>
-  </si>
-  <si>
-    <t>0.7306,0.0947,0.1327,0.0112</t>
-  </si>
-  <si>
-    <t>0.6781,0.1651,0.0432,0.0176</t>
-  </si>
-  <si>
-    <t>0.1837,0.1531,0.8550,0.0017</t>
-  </si>
-  <si>
-    <t>0.8231,0.0557,0.0274,0.0110</t>
-  </si>
-  <si>
-    <t>0.7951,0.0603,0.0397,0.0157</t>
-  </si>
-  <si>
-    <t>0.7066,0.1491,0.0868,0.0133</t>
-  </si>
-  <si>
-    <t>0.7660,0.0300,0.1801,0.0002</t>
-  </si>
-  <si>
-    <t>0.7533,0.0140,0.3257,0.0003</t>
-  </si>
-  <si>
-    <t>0.7251,0.0147,0.3556,0.0007</t>
-  </si>
-  <si>
-    <t>0.6763,0.1042,0.1813,0.0002</t>
-  </si>
-  <si>
-    <t>0.5278,0.0056,0.7186,0.0002</t>
-  </si>
-  <si>
-    <t>0.8616,0.1278,0.0205,0.0009</t>
-  </si>
-  <si>
-    <t>0.0090,0.9914,0.0254,0.0001</t>
-  </si>
-  <si>
-    <t>0.9192,0.0247,0.0143,0.0037</t>
-  </si>
-  <si>
-    <t>0.9177,0.0299,0.0459,0.0005</t>
-  </si>
-  <si>
-    <t>0.3239,0.1486,0.7094,0.0014</t>
-  </si>
-  <si>
-    <t>0.6784,0.0605,0.2516,0.0004</t>
-  </si>
-  <si>
-    <t>0.9096,0.0126,0.0735,0.0000</t>
-  </si>
-  <si>
-    <t>0.3204,0.6785,0.0334,0.0000</t>
-  </si>
-  <si>
-    <t>0.4750,0.3427,0.0914,0.0001</t>
-  </si>
-  <si>
-    <t>0.9476,0.0255,0.0143,0.0006</t>
-  </si>
-  <si>
-    <t>0.8152,0.0361,0.0312,0.0232</t>
-  </si>
-  <si>
-    <t>0.9414,0.0315,0.0131,0.0019</t>
-  </si>
-  <si>
-    <t>0.9505,0.0153,0.0110,0.0029</t>
-  </si>
-  <si>
-    <t>0.9333,0.0125,0.0150,0.0041</t>
-  </si>
-  <si>
-    <t>0.9610,0.0159,0.0092,0.0006</t>
-  </si>
-  <si>
-    <t>0.7650,0.0969,0.1300,0.0002</t>
-  </si>
-  <si>
-    <t>0.8999,0.0067,0.1120,0.0004</t>
-  </si>
-  <si>
-    <t>0.5070,0.0489,0.5462,0.0005</t>
-  </si>
-  <si>
-    <t>0.8047,0.0094,0.2780,0.0002</t>
-  </si>
-  <si>
-    <t>0.5390,0.0427,0.4817,0.0002</t>
-  </si>
-  <si>
-    <t>0.6380,0.0703,0.2399,0.0003</t>
-  </si>
-  <si>
-    <t>0.8305,0.0639,0.0660,0.0064</t>
-  </si>
-  <si>
-    <t>0.8322,0.0764,0.0243,0.0066</t>
-  </si>
-  <si>
-    <t>0.7285,0.1358,0.0453,0.0162</t>
-  </si>
-  <si>
-    <t>0.8722,0.0621,0.0263,0.0063</t>
-  </si>
-  <si>
-    <t>0.7219,0.1112,0.0597,0.0119</t>
-  </si>
-  <si>
-    <t>0.8707,0.0197,0.0212,0.0171</t>
-  </si>
-  <si>
-    <t>0.7531,0.0535,0.0414,0.0312</t>
-  </si>
-  <si>
-    <t>0.7661,0.0968,0.0548,0.0148</t>
-  </si>
-  <si>
-    <t>0.7436,0.0668,0.0828,0.0251</t>
-  </si>
-  <si>
-    <t>0.6947,0.1123,0.0773,0.0252</t>
-  </si>
-  <si>
-    <t>0.7460,0.0471,0.0376,0.0375</t>
-  </si>
-  <si>
-    <t>0.8211,0.0767,0.0254,0.0072</t>
-  </si>
-  <si>
-    <t>0.7853,0.0282,0.0223,0.0367</t>
-  </si>
-  <si>
-    <t>0.8623,0.0250,0.0180,0.0131</t>
-  </si>
-  <si>
-    <t>0.7972,0.0666,0.0547,0.0112</t>
-  </si>
-  <si>
-    <t>0.7565,0.0293,0.0351,0.0455</t>
-  </si>
-  <si>
-    <t>0.1083,0.0146,0.9624,0.0001</t>
-  </si>
-  <si>
-    <t>0.9615,0.0052,0.0281,0.0001</t>
-  </si>
-  <si>
-    <t>0.9591,0.0080,0.0206,0.0004</t>
-  </si>
-  <si>
-    <t>0.9655,0.0010,0.0221,0.0004</t>
-  </si>
-  <si>
-    <t>0.5152,0.5248,0.0767,0.0032</t>
-  </si>
-  <si>
-    <t>0.8119,0.1726,0.0396,0.0013</t>
-  </si>
-  <si>
-    <t>0.6579,0.2604,0.0892,0.0042</t>
-  </si>
-  <si>
-    <t>0.4746,0.4264,0.1757,0.0040</t>
-  </si>
-  <si>
-    <t>0.6104,0.4485,0.0548,0.0023</t>
-  </si>
-  <si>
-    <t>0.8448,0.1639,0.0349,0.0010</t>
-  </si>
-  <si>
-    <t>0.7484,0.1829,0.0785,0.0026</t>
-  </si>
-  <si>
-    <t>0.8656,0.0795,0.0439,0.0010</t>
-  </si>
-  <si>
-    <t>0.9094,0.0146,0.0857,0.0003</t>
-  </si>
-  <si>
-    <t>0.9298,0.0149,0.0462,0.0007</t>
-  </si>
-  <si>
-    <t>0.8350,0.0709,0.0878,0.0017</t>
-  </si>
-  <si>
-    <t>0.9482,0.0160,0.0187,0.0008</t>
-  </si>
-  <si>
-    <t>0.3255,0.7316,0.1045,0.0009</t>
-  </si>
-  <si>
-    <t>0.4248,0.6925,0.0375,0.0006</t>
-  </si>
-  <si>
-    <t>0.8503,0.1416,0.0267,0.0009</t>
-  </si>
-  <si>
-    <t>0.1403,0.8354,0.2799,0.0014</t>
-  </si>
-  <si>
-    <t>0.8722,0.0620,0.0462,0.0007</t>
-  </si>
-  <si>
-    <t>0.7943,0.0956,0.0615,0.0058</t>
-  </si>
-  <si>
-    <t>0.8201,0.1032,0.0660,0.0028</t>
-  </si>
-  <si>
-    <t>0.8399,0.0640,0.0428,0.0057</t>
-  </si>
-  <si>
-    <t>0.7862,0.0576,0.0306,0.0216</t>
-  </si>
-  <si>
-    <t>0.8435,0.0482,0.0214,0.0111</t>
-  </si>
-  <si>
-    <t>0.8678,0.0721,0.0330,0.0024</t>
-  </si>
-  <si>
-    <t>0.8281,0.0309,0.0202,0.0268</t>
-  </si>
-  <si>
-    <t>0.7445,0.1644,0.0549,0.0076</t>
-  </si>
-  <si>
-    <t>0.7870,0.0331,0.0255,0.0445</t>
-  </si>
-  <si>
-    <t>0.7302,0.1563,0.0735,0.0110</t>
-  </si>
-  <si>
-    <t>0.9490,0.0116,0.0232,0.0001</t>
-  </si>
-  <si>
-    <t>0.8878,0.0024,0.1675,0.0001</t>
-  </si>
-  <si>
-    <t>0.5363,0.0291,0.5266,0.0003</t>
-  </si>
-  <si>
-    <t>0.8937,0.0202,0.1119,0.0008</t>
-  </si>
-  <si>
-    <t>0.9114,0.0364,0.0401,0.0004</t>
-  </si>
-  <si>
-    <t>0.8836,0.0723,0.0367,0.0003</t>
-  </si>
-  <si>
-    <t>0.9391,0.0090,0.0435,0.0005</t>
-  </si>
-  <si>
-    <t>0.9012,0.0297,0.0580,0.0008</t>
-  </si>
-  <si>
-    <t>0.9643,0.0117,0.0100,0.0005</t>
-  </si>
-  <si>
-    <t>0.8870,0.0163,0.0209,0.0143</t>
-  </si>
-  <si>
-    <t>0.9314,0.0206,0.0259,0.0014</t>
-  </si>
-  <si>
-    <t>0.9060,0.0096,0.0180,0.0094</t>
-  </si>
-  <si>
-    <t>0.8313,0.0257,0.1824,0.0010</t>
-  </si>
-  <si>
-    <t>0.7996,0.1552,0.0472,0.0027</t>
-  </si>
-  <si>
-    <t>0.7626,0.0977,0.0576,0.0164</t>
-  </si>
-  <si>
-    <t>0.8110,0.0606,0.0362,0.0131</t>
-  </si>
-  <si>
-    <t>0.7844,0.0444,0.0395,0.0215</t>
-  </si>
-  <si>
-    <t>0.7328,0.1960,0.0771,0.0046</t>
-  </si>
-  <si>
-    <t>0.9035,0.0454,0.0236,0.0019</t>
-  </si>
-  <si>
-    <t>0.5714,0.1280,0.0295,0.0335</t>
-  </si>
-  <si>
-    <t>0.3257,0.1176,0.6949,0.0087</t>
-  </si>
-  <si>
-    <t>0.8982,0.0278,0.0278,0.0060</t>
-  </si>
-  <si>
-    <t>0.8369,0.0801,0.0462,0.0042</t>
-  </si>
-  <si>
-    <t>0.6611,0.3156,0.0969,0.0016</t>
-  </si>
-  <si>
-    <t>0.8982,0.0510,0.0341,0.0008</t>
-  </si>
-  <si>
-    <t>0.9012,0.0535,0.0252,0.0011</t>
-  </si>
-  <si>
-    <t>0.6638,0.3459,0.0688,0.0047</t>
-  </si>
-  <si>
-    <t>0.8170,0.1526,0.0515,0.0009</t>
-  </si>
-  <si>
-    <t>0.8686,0.0706,0.0704,0.0016</t>
-  </si>
-  <si>
-    <t>0.6828,0.1462,0.0736,0.0166</t>
-  </si>
-  <si>
-    <t>0.7957,0.0721,0.0452,0.0150</t>
-  </si>
-  <si>
-    <t>0.8035,0.1011,0.0371,0.0071</t>
-  </si>
-  <si>
-    <t>0.8596,0.0378,0.0290,0.0088</t>
-  </si>
-  <si>
-    <t>0.7340,0.1866,0.0856,0.0042</t>
-  </si>
-  <si>
-    <t>0.6136,0.1291,0.0598,0.0358</t>
-  </si>
-  <si>
-    <t>0.7019,0.1317,0.0254,0.0134</t>
-  </si>
-  <si>
-    <t>0.8239,0.0316,0.0304,0.0278</t>
-  </si>
-  <si>
-    <t>0.7943,0.0820,0.0883,0.0062</t>
-  </si>
-  <si>
-    <t>0.8278,0.1148,0.0376,0.0033</t>
-  </si>
-  <si>
-    <t>0.6996,0.2167,0.0838,0.0031</t>
-  </si>
-  <si>
-    <t>0.7843,0.0886,0.0294,0.0056</t>
-  </si>
-  <si>
-    <t>0.7586,0.0926,0.0683,0.0140</t>
-  </si>
-  <si>
-    <t>0.8624,0.0346,0.0323,0.0086</t>
-  </si>
-  <si>
-    <t>0.6756,0.1467,0.1261,0.0287</t>
-  </si>
-  <si>
-    <t>0.6872,0.0990,0.1018,0.0296</t>
-  </si>
-  <si>
-    <t>0.4314,0.0297,0.7475,0.0009</t>
-  </si>
-  <si>
-    <t>0.5736,0.3140,0.0780,0.0142</t>
-  </si>
-  <si>
-    <t>0.7762,0.0195,0.2616,0.0005</t>
-  </si>
-  <si>
-    <t>0.9541,0.0036,0.0494,0.0002</t>
-  </si>
-  <si>
-    <t>0.9167,0.0130,0.0765,0.0002</t>
-  </si>
-  <si>
-    <t>0.8107,0.0226,0.1527,0.0006</t>
-  </si>
-  <si>
-    <t>0.9325,0.0070,0.0685,0.0001</t>
-  </si>
-  <si>
-    <t>0.9309,0.0025,0.0859,0.0001</t>
-  </si>
-  <si>
-    <t>0.5886,0.0147,0.6036,0.0003</t>
-  </si>
-  <si>
-    <t>0.8888,0.0198,0.1084,0.0005</t>
-  </si>
-  <si>
-    <t>0.9225,0.0226,0.0438,0.0007</t>
-  </si>
-  <si>
-    <t>0.6538,0.1932,0.1232,0.0002</t>
-  </si>
-  <si>
-    <t>0.7696,0.1314,0.1287,0.0011</t>
-  </si>
-  <si>
-    <t>0.9535,0.0167,0.0214,0.0002</t>
-  </si>
-  <si>
-    <t>0.9660,0.0096,0.0134,0.0002</t>
-  </si>
-  <si>
-    <t>0.9585,0.0097,0.0167,0.0004</t>
-  </si>
-  <si>
-    <t>0.9288,0.0319,0.0232,0.0007</t>
-  </si>
-  <si>
-    <t>0.7133,0.1251,0.0411,0.0146</t>
-  </si>
-  <si>
-    <t>0.6781,0.2092,0.0684,0.0109</t>
-  </si>
-  <si>
-    <t>0.8094,0.0796,0.0747,0.0071</t>
-  </si>
-  <si>
-    <t>0.5962,0.1551,0.0609,0.0315</t>
-  </si>
-  <si>
-    <t>0.4417,0.0875,0.0517,0.1594</t>
-  </si>
-  <si>
-    <t>0.9563,0.0140,0.0181,0.0002</t>
-  </si>
-  <si>
-    <t>0.9617,0.0086,0.0250,0.0001</t>
-  </si>
-  <si>
-    <t>0.9847,0.0035,0.0062,0.0002</t>
-  </si>
-  <si>
-    <t>0.9483,0.0069,0.0478,0.0001</t>
-  </si>
-  <si>
-    <t>0.9552,0.0094,0.0346,0.0002</t>
-  </si>
-  <si>
-    <t>0.8656,0.0394,0.0838,0.0016</t>
-  </si>
-  <si>
-    <t>0.9421,0.0047,0.0625,0.0003</t>
-  </si>
-  <si>
-    <t>0.9894,0.0007,0.0060,0.0001</t>
-  </si>
-  <si>
-    <t>0.9258,0.0020,0.0497,0.0005</t>
-  </si>
-  <si>
-    <t>0.8258,0.0171,0.1638,0.0002</t>
-  </si>
-  <si>
-    <t>0.7459,0.0833,0.0382,0.0161</t>
-  </si>
-  <si>
-    <t>0.8073,0.0599,0.0400,0.0144</t>
-  </si>
-  <si>
-    <t>0.7422,0.1620,0.0704,0.0063</t>
-  </si>
-  <si>
-    <t>0.7193,0.1088,0.1012,0.0162</t>
-  </si>
-  <si>
-    <t>0.6990,0.0644,0.0536,0.0370</t>
-  </si>
-  <si>
-    <t>0.8440,0.0540,0.0279,0.0097</t>
-  </si>
-  <si>
-    <t>0.7987,0.0412,0.0210,0.0226</t>
-  </si>
-  <si>
-    <t>0.8483,0.0465,0.0277,0.0095</t>
-  </si>
-  <si>
-    <t>0.8057,0.0528,0.1469,0.0016</t>
-  </si>
-  <si>
-    <t>0.8799,0.0426,0.0665,0.0018</t>
-  </si>
-  <si>
-    <t>0.8623,0.0810,0.0383,0.0030</t>
-  </si>
-  <si>
-    <t>0.9468,0.0010,0.0805,0.0002</t>
-  </si>
-  <si>
-    <t>0.7606,0.0050,0.3179,0.0013</t>
-  </si>
-  <si>
-    <t>0.9719,0.0063,0.0182,0.0001</t>
-  </si>
-  <si>
-    <t>0.8991,0.0017,0.1600,0.0002</t>
-  </si>
-  <si>
-    <t>0.9780,0.0011,0.0246,0.0000</t>
-  </si>
-  <si>
-    <t>0.5253,0.0033,0.7117,0.0004</t>
-  </si>
-  <si>
-    <t>0.8966,0.0053,0.1244,0.0002</t>
-  </si>
-  <si>
-    <t>0.9354,0.0053,0.0751,0.0001</t>
-  </si>
-  <si>
-    <t>0.8982,0.0155,0.1108,0.0006</t>
-  </si>
-  <si>
-    <t>0.9697,0.0057,0.0181,0.0002</t>
-  </si>
-  <si>
-    <t>0.9183,0.0141,0.0539,0.0015</t>
-  </si>
-  <si>
-    <t>0.7613,0.0803,0.0432,0.0191</t>
-  </si>
-  <si>
-    <t>0.8564,0.0829,0.0209,0.0033</t>
-  </si>
-  <si>
-    <t>0.8819,0.0278,0.0265,0.0090</t>
-  </si>
-  <si>
-    <t>0.7926,0.0670,0.0683,0.0072</t>
-  </si>
-  <si>
-    <t>0.7569,0.0510,0.0403,0.0295</t>
-  </si>
-  <si>
-    <t>0.6715,0.0893,0.0291,0.0369</t>
-  </si>
-  <si>
-    <t>0.6919,0.1145,0.0732,0.0366</t>
-  </si>
-  <si>
-    <t>0.7513,0.1030,0.0416,0.0101</t>
-  </si>
-  <si>
-    <t>0.9653,0.0045,0.0222,0.0001</t>
-  </si>
-  <si>
-    <t>0.7679,0.0271,0.1806,0.0002</t>
-  </si>
-  <si>
-    <t>0.8415,0.0071,0.1755,0.0001</t>
-  </si>
-  <si>
-    <t>0.9370,0.0144,0.0505,0.0003</t>
-  </si>
-  <si>
-    <t>0.8823,0.0045,0.1781,0.0003</t>
-  </si>
-  <si>
-    <t>0.9724,0.0023,0.0143,0.0004</t>
-  </si>
-  <si>
-    <t>0.8473,0.0164,0.2039,0.0005</t>
-  </si>
-  <si>
-    <t>0.9558,0.0051,0.0207,0.0006</t>
-  </si>
-  <si>
-    <t>0.8586,0.0375,0.0395,0.0063</t>
-  </si>
-  <si>
-    <t>0.9246,0.0172,0.0172,0.0035</t>
-  </si>
-  <si>
-    <t>0.9676,0.0126,0.0054,0.0005</t>
-  </si>
-  <si>
-    <t>0.9095,0.0183,0.0308,0.0047</t>
-  </si>
-  <si>
-    <t>0.8744,0.0210,0.0244,0.0119</t>
-  </si>
-  <si>
-    <t>0.9023,0.0322,0.0504,0.0013</t>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0.9532,0.0149,0.0076,0.0202</t>
+  </si>
+  <si>
+    <t>0.0087,0.0002,0.0003,0.9974</t>
+  </si>
+  <si>
+    <t>0.9439,0.0026,0.0054,0.0224</t>
+  </si>
+  <si>
+    <t>0.1836,0.0025,0.0156,0.8902</t>
+  </si>
+  <si>
+    <t>0.9933,0.0008,0.0018,0.0013</t>
+  </si>
+  <si>
+    <t>0.9904,0.0009,0.0007,0.0039</t>
+  </si>
+  <si>
+    <t>0.9960,0.0003,0.0002,0.0020</t>
+  </si>
+  <si>
+    <t>0.9977,0.0003,0.0001,0.0008</t>
+  </si>
+  <si>
+    <t>0.9854,0.0040,0.0015,0.0050</t>
+  </si>
+  <si>
+    <t>0.9828,0.0130,0.0025,0.0020</t>
+  </si>
+  <si>
+    <t>0.9939,0.0013,0.0013,0.0011</t>
+  </si>
+  <si>
+    <t>0.9902,0.0005,0.0008,0.0055</t>
+  </si>
+  <si>
+    <t>0.7043,0.0961,0.2355,0.0127</t>
+  </si>
+  <si>
+    <t>0.0539,0.0362,0.9127,0.0030</t>
+  </si>
+  <si>
+    <t>0.5351,0.0014,0.7166,0.0006</t>
+  </si>
+  <si>
+    <t>0.0052,0.0021,0.9943,0.0006</t>
+  </si>
+  <si>
+    <t>0.9615,0.0070,0.0180,0.0033</t>
+  </si>
+  <si>
+    <t>0.0003,0.9991,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.0018,0.9950,0.0023,0.0023</t>
+  </si>
+  <si>
+    <t>0.1357,0.8808,0.0089,0.0035</t>
+  </si>
+  <si>
+    <t>0.0034,0.9918,0.0035,0.0009</t>
+  </si>
+  <si>
+    <t>0.0010,0.9973,0.0016,0.0005</t>
+  </si>
+  <si>
+    <t>0.8402,0.0034,0.0961,0.0265</t>
+  </si>
+  <si>
+    <t>0.5140,0.0120,0.6092,0.0081</t>
+  </si>
+  <si>
+    <t>0.0057,0.0011,0.9936,0.0021</t>
+  </si>
+  <si>
+    <t>0.0827,0.0022,0.9617,0.0026</t>
+  </si>
+  <si>
+    <t>0.0537,0.0018,0.9785,0.0005</t>
+  </si>
+  <si>
+    <t>0.0800,0.0057,0.9136,0.0474</t>
+  </si>
+  <si>
+    <t>0.0033,0.0012,0.9927,0.0066</t>
+  </si>
+  <si>
+    <t>0.8240,0.2613,0.0066,0.0022</t>
+  </si>
+  <si>
+    <t>0.7455,0.1405,0.1022,0.0085</t>
+  </si>
+  <si>
+    <t>0.0018,0.0064,0.9916,0.0133</t>
+  </si>
+  <si>
+    <t>0.0023,0.8001,0.6325,0.0001</t>
+  </si>
+  <si>
+    <t>0.9020,0.0140,0.0234,0.0580</t>
+  </si>
+  <si>
+    <t>0.7112,0.0609,0.1563,0.0495</t>
+  </si>
+  <si>
+    <t>0.7284,0.3169,0.0158,0.0037</t>
+  </si>
+  <si>
+    <t>0.0458,0.9337,0.2975,0.0026</t>
+  </si>
+  <si>
+    <t>0.0723,0.2042,0.8157,0.0192</t>
+  </si>
+  <si>
+    <t>0.0413,0.0033,0.9763,0.0010</t>
+  </si>
+  <si>
+    <t>0.1265,0.0363,0.8908,0.0097</t>
+  </si>
+  <si>
+    <t>0.0550,0.0003,0.9441,0.0073</t>
+  </si>
+  <si>
+    <t>0.0109,0.0038,0.9901,0.0012</t>
+  </si>
+  <si>
+    <t>0.0085,0.9690,0.0258,0.0031</t>
+  </si>
+  <si>
+    <t>0.0635,0.0111,0.9562,0.0039</t>
+  </si>
+  <si>
+    <t>0.0129,0.8924,0.0056,0.7194</t>
+  </si>
+  <si>
+    <t>0.0014,0.9851,0.0051,0.0693</t>
+  </si>
+  <si>
+    <t>0.0003,0.9980,0.0194,0.0003</t>
+  </si>
+  <si>
+    <t>0.0009,0.9927,0.0068,0.0081</t>
+  </si>
+  <si>
+    <t>0.0014,0.0391,0.9850,0.0066</t>
+  </si>
+  <si>
+    <t>0.0012,0.1900,0.9955,0.0002</t>
+  </si>
+  <si>
+    <t>0.2209,0.0205,0.8354,0.0092</t>
+  </si>
+  <si>
+    <t>0.1141,0.0024,0.9117,0.0087</t>
+  </si>
+  <si>
+    <t>0.0109,0.0067,0.9784,0.0120</t>
+  </si>
+  <si>
+    <t>0.0443,0.0400,0.9469,0.0158</t>
+  </si>
+  <si>
+    <t>0.9443,0.0690,0.0018,0.0026</t>
+  </si>
+  <si>
+    <t>0.9345,0.0039,0.0626,0.0036</t>
+  </si>
+  <si>
+    <t>0.9380,0.0319,0.0202,0.0141</t>
+  </si>
+  <si>
+    <t>0.0294,0.1641,0.9591,0.0149</t>
+  </si>
+  <si>
+    <t>0.9941,0.0015,0.0009,0.0014</t>
+  </si>
+  <si>
+    <t>0.9827,0.0056,0.0042,0.0050</t>
+  </si>
+  <si>
+    <t>0.9736,0.0289,0.0030,0.0009</t>
+  </si>
+  <si>
+    <t>0.0016,0.6666,0.9837,0.0004</t>
+  </si>
+  <si>
+    <t>0.0021,0.0103,0.9952,0.0014</t>
+  </si>
+  <si>
+    <t>0.0115,0.5585,0.8332,0.0199</t>
+  </si>
+  <si>
+    <t>0.0000,0.9963,0.9674,0.0000</t>
+  </si>
+  <si>
+    <t>0.0020,0.0132,0.9959,0.0009</t>
+  </si>
+  <si>
+    <t>0.0249,0.9606,0.0097,0.0032</t>
+  </si>
+  <si>
+    <t>0.0421,0.9621,0.0028,0.0001</t>
+  </si>
+  <si>
+    <t>0.9286,0.0104,0.0724,0.0059</t>
+  </si>
+  <si>
+    <t>0.7158,0.0287,0.3479,0.0188</t>
+  </si>
+  <si>
+    <t>0.0055,0.0339,0.9890,0.0077</t>
+  </si>
+  <si>
+    <t>0.0006,0.9548,0.9641,0.0002</t>
+  </si>
+  <si>
+    <t>0.0008,0.9910,0.4872,0.0001</t>
+  </si>
+  <si>
+    <t>0.0025,0.9784,0.2201,0.0002</t>
+  </si>
+  <si>
+    <t>0.0073,0.8874,0.7189,0.0027</t>
+  </si>
+  <si>
+    <t>0.0165,0.0071,0.0427,0.9738</t>
+  </si>
+  <si>
+    <t>0.0004,0.0007,0.0009,0.9993</t>
+  </si>
+  <si>
+    <t>0.0014,0.0005,0.0002,0.9993</t>
+  </si>
+  <si>
+    <t>0.0022,0.0003,0.0025,0.9980</t>
+  </si>
+  <si>
+    <t>0.0030,0.0048,0.0024,0.9963</t>
+  </si>
+  <si>
+    <t>0.0059,0.0007,0.0008,0.9967</t>
+  </si>
+  <si>
+    <t>0.0014,0.9810,0.7174,0.0007</t>
+  </si>
+  <si>
+    <t>0.0017,0.5370,0.9882,0.0002</t>
+  </si>
+  <si>
+    <t>0.0045,0.8101,0.8022,0.0029</t>
+  </si>
+  <si>
+    <t>0.0215,0.4560,0.9154,0.0025</t>
+  </si>
+  <si>
+    <t>0.0001,0.9837,0.9845,0.0000</t>
+  </si>
+  <si>
+    <t>0.0061,0.9263,0.2369,0.0003</t>
+  </si>
+  <si>
+    <t>0.9918,0.0047,0.0007,0.0009</t>
+  </si>
+  <si>
+    <t>0.9271,0.0884,0.0030,0.0044</t>
+  </si>
+  <si>
+    <t>0.9725,0.0306,0.0036,0.0023</t>
+  </si>
+  <si>
+    <t>0.9908,0.0034,0.0008,0.0014</t>
+  </si>
+  <si>
+    <t>0.9834,0.0136,0.0006,0.0009</t>
+  </si>
+  <si>
+    <t>0.9723,0.0138,0.0011,0.0038</t>
+  </si>
+  <si>
+    <t>0.9631,0.0274,0.0043,0.0041</t>
+  </si>
+  <si>
+    <t>0.9887,0.0033,0.0011,0.0030</t>
+  </si>
+  <si>
+    <t>0.9982,0.0003,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9923,0.0019,0.0016,0.0012</t>
+  </si>
+  <si>
+    <t>0.9957,0.0003,0.0001,0.0027</t>
+  </si>
+  <si>
+    <t>0.9986,0.0001,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9960,0.0003,0.0002,0.0015</t>
+  </si>
+  <si>
+    <t>0.9789,0.0099,0.0010,0.0048</t>
+  </si>
+  <si>
+    <t>0.9906,0.0021,0.0019,0.0021</t>
+  </si>
+  <si>
+    <t>0.9956,0.0004,0.0006,0.0013</t>
+  </si>
+  <si>
+    <t>0.0023,0.0007,0.9961,0.0032</t>
+  </si>
+  <si>
+    <t>0.0733,0.0060,0.9682,0.0021</t>
+  </si>
+  <si>
+    <t>0.9937,0.0006,0.0010,0.0008</t>
+  </si>
+  <si>
+    <t>0.0159,0.0010,0.9820,0.0095</t>
+  </si>
+  <si>
+    <t>0.0081,0.9853,0.0015,0.0023</t>
+  </si>
+  <si>
+    <t>0.0241,0.9699,0.0081,0.0032</t>
+  </si>
+  <si>
+    <t>0.0316,0.9609,0.0035,0.0035</t>
+  </si>
+  <si>
+    <t>0.0086,0.9845,0.0041,0.0030</t>
+  </si>
+  <si>
+    <t>0.0008,0.9967,0.0040,0.0018</t>
+  </si>
+  <si>
+    <t>0.0019,0.9948,0.0006,0.0010</t>
+  </si>
+  <si>
+    <t>0.7952,0.3155,0.0028,0.0007</t>
+  </si>
+  <si>
+    <t>0.9110,0.0053,0.0443,0.0136</t>
+  </si>
+  <si>
+    <t>0.1875,0.0046,0.8964,0.0047</t>
+  </si>
+  <si>
+    <t>0.2348,0.0384,0.7239,0.0437</t>
+  </si>
+  <si>
+    <t>0.5347,0.0260,0.5798,0.0069</t>
+  </si>
+  <si>
+    <t>0.0513,0.0162,0.0741,0.9321</t>
+  </si>
+  <si>
+    <t>0.0033,0.9919,0.0183,0.0010</t>
+  </si>
+  <si>
+    <t>0.0108,0.9619,0.0359,0.0106</t>
+  </si>
+  <si>
+    <t>0.0008,0.9957,0.0034,0.0014</t>
+  </si>
+  <si>
+    <t>0.0029,0.9657,0.7522,0.0011</t>
+  </si>
+  <si>
+    <t>0.0101,0.9862,0.0332,0.0006</t>
+  </si>
+  <si>
+    <t>0.8661,0.1173,0.0383,0.0077</t>
+  </si>
+  <si>
+    <t>0.8850,0.1144,0.0120,0.0121</t>
+  </si>
+  <si>
+    <t>0.9877,0.0026,0.0008,0.0052</t>
+  </si>
+  <si>
+    <t>0.9940,0.0004,0.0003,0.0043</t>
+  </si>
+  <si>
+    <t>0.9863,0.0021,0.0008,0.0056</t>
+  </si>
+  <si>
+    <t>0.9871,0.0039,0.0030,0.0025</t>
+  </si>
+  <si>
+    <t>0.9967,0.0001,0.0001,0.0027</t>
+  </si>
+  <si>
+    <t>0.9871,0.0076,0.0022,0.0009</t>
+  </si>
+  <si>
+    <t>0.9901,0.0009,0.0005,0.0052</t>
+  </si>
+  <si>
+    <t>0.9734,0.0033,0.0096,0.0080</t>
+  </si>
+  <si>
+    <t>0.0022,0.5266,0.9576,0.0011</t>
+  </si>
+  <si>
+    <t>0.0019,0.8739,0.9047,0.0003</t>
+  </si>
+  <si>
+    <t>0.0183,0.0490,0.9684,0.0021</t>
+  </si>
+  <si>
+    <t>0.0212,0.0190,0.9794,0.0010</t>
+  </si>
+  <si>
+    <t>0.9900,0.0037,0.0023,0.0006</t>
+  </si>
+  <si>
+    <t>0.8301,0.0236,0.0755,0.0660</t>
+  </si>
+  <si>
+    <t>0.0616,0.0017,0.9749,0.0033</t>
+  </si>
+  <si>
+    <t>0.8160,0.0186,0.2160,0.0040</t>
+  </si>
+  <si>
+    <t>0.0065,0.0005,0.0071,0.9933</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0001,0.9999</t>
+  </si>
+  <si>
+    <t>0.0006,0.0008,0.0012,0.9993</t>
+  </si>
+  <si>
+    <t>0.0026,0.0001,0.0005,0.9987</t>
+  </si>
+  <si>
+    <t>0.0014,0.6796,0.9693,0.0014</t>
+  </si>
+  <si>
+    <t>0.9915,0.0016,0.0018,0.0017</t>
+  </si>
+  <si>
+    <t>0.1192,0.8609,0.0099,0.0387</t>
+  </si>
+  <si>
+    <t>0.9780,0.0027,0.0016,0.0129</t>
+  </si>
+  <si>
+    <t>0.6763,0.3652,0.0107,0.0109</t>
+  </si>
+  <si>
+    <t>0.9974,0.0002,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9007,0.0037,0.0273,0.0424</t>
+  </si>
+  <si>
+    <t>0.9437,0.0016,0.0046,0.0303</t>
+  </si>
+  <si>
+    <t>0.0009,0.0286,0.9737,0.0475</t>
+  </si>
+  <si>
+    <t>0.9830,0.0009,0.0007,0.0131</t>
+  </si>
+  <si>
+    <t>0.7762,0.0020,0.0024,0.3133</t>
+  </si>
+  <si>
+    <t>0.7524,0.2825,0.0235,0.0095</t>
+  </si>
+  <si>
+    <t>0.7089,0.0814,0.0339,0.1232</t>
+  </si>
+  <si>
+    <t>0.9723,0.0125,0.0067,0.0035</t>
+  </si>
+  <si>
+    <t>0.2207,0.5993,0.2078,0.0275</t>
+  </si>
+  <si>
+    <t>0.8807,0.0608,0.0404,0.0128</t>
+  </si>
+  <si>
+    <t>0.9887,0.0090,0.0017,0.0004</t>
+  </si>
+  <si>
+    <t>0.9587,0.0037,0.0173,0.0088</t>
+  </si>
+  <si>
+    <t>0.9924,0.0009,0.0004,0.0032</t>
+  </si>
+  <si>
+    <t>0.9918,0.0012,0.0010,0.0025</t>
+  </si>
+  <si>
+    <t>0.9724,0.0004,0.0007,0.0323</t>
+  </si>
+  <si>
+    <t>0.9934,0.0008,0.0011,0.0013</t>
+  </si>
+  <si>
+    <t>0.9923,0.0009,0.0006,0.0029</t>
+  </si>
+  <si>
+    <t>0.9802,0.0083,0.0054,0.0040</t>
+  </si>
+  <si>
+    <t>0.9958,0.0002,0.0004,0.0016</t>
+  </si>
+  <si>
+    <t>0.8327,0.1818,0.0195,0.0078</t>
+  </si>
+  <si>
+    <t>0.9114,0.1149,0.0028,0.0008</t>
+  </si>
+  <si>
+    <t>0.8782,0.1363,0.0067,0.0023</t>
+  </si>
+  <si>
+    <t>0.6684,0.2232,0.0666,0.0249</t>
+  </si>
+  <si>
+    <t>0.9977,0.0006,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9315,0.0331,0.0271,0.0052</t>
+  </si>
+  <si>
+    <t>0.9821,0.0052,0.0024,0.0046</t>
+  </si>
+  <si>
+    <t>0.9769,0.0018,0.0004,0.0160</t>
+  </si>
+  <si>
+    <t>0.0031,0.0198,0.9973,0.0004</t>
+  </si>
+  <si>
+    <t>0.9720,0.0183,0.0069,0.0021</t>
+  </si>
+  <si>
+    <t>0.0033,0.0016,0.9892,0.0193</t>
+  </si>
+  <si>
+    <t>0.0056,0.0147,0.9852,0.0063</t>
+  </si>
+  <si>
+    <t>0.0315,0.0014,0.9867,0.0010</t>
+  </si>
+  <si>
+    <t>0.0074,0.0108,0.9891,0.0030</t>
+  </si>
+  <si>
+    <t>0.0117,0.0096,0.9906,0.0009</t>
+  </si>
+  <si>
+    <t>0.0097,0.0017,0.9891,0.0040</t>
+  </si>
+  <si>
+    <t>0.0032,0.0076,0.9894,0.0124</t>
+  </si>
+  <si>
+    <t>0.5991,0.0443,0.4133,0.0165</t>
+  </si>
+  <si>
+    <t>0.3005,0.0129,0.8194,0.0027</t>
+  </si>
+  <si>
+    <t>0.1931,0.0475,0.7975,0.0071</t>
+  </si>
+  <si>
+    <t>0.4967,0.0101,0.6798,0.0017</t>
+  </si>
+  <si>
+    <t>0.3749,0.0429,0.6769,0.0047</t>
+  </si>
+  <si>
+    <t>0.2379,0.0879,0.6100,0.0073</t>
+  </si>
+  <si>
+    <t>0.6493,0.0615,0.3868,0.0227</t>
+  </si>
+  <si>
+    <t>0.3841,0.0897,0.5742,0.0313</t>
+  </si>
+  <si>
+    <t>0.5540,0.5641,0.0071,0.0016</t>
+  </si>
+  <si>
+    <t>0.0160,0.9822,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.9277,0.0997,0.0019,0.0022</t>
+  </si>
+  <si>
+    <t>0.4736,0.6612,0.0027,0.0018</t>
+  </si>
+  <si>
+    <t>0.8831,0.1591,0.0078,0.0047</t>
+  </si>
+  <si>
+    <t>0.8610,0.0132,0.0945,0.0182</t>
+  </si>
+  <si>
+    <t>0.8057,0.0026,0.2518,0.0036</t>
+  </si>
+  <si>
+    <t>0.7453,0.0044,0.0816,0.1000</t>
+  </si>
+  <si>
+    <t>0.8032,0.0064,0.2683,0.0065</t>
+  </si>
+  <si>
+    <t>0.7684,0.0038,0.1267,0.0225</t>
+  </si>
+  <si>
+    <t>0.0079,0.0056,0.9863,0.0080</t>
+  </si>
+  <si>
+    <t>0.1131,0.0480,0.8909,0.0122</t>
+  </si>
+  <si>
+    <t>0.1158,0.0193,0.7255,0.1425</t>
+  </si>
+  <si>
+    <t>0.0520,0.0015,0.9574,0.0050</t>
+  </si>
+  <si>
+    <t>0.0061,0.0178,0.9815,0.0034</t>
+  </si>
+  <si>
+    <t>0.9874,0.0013,0.0004,0.0077</t>
+  </si>
+  <si>
+    <t>0.9951,0.0009,0.0003,0.0015</t>
+  </si>
+  <si>
+    <t>0.8748,0.1248,0.0108,0.0147</t>
+  </si>
+  <si>
+    <t>0.9398,0.0663,0.0051,0.0067</t>
+  </si>
+  <si>
+    <t>0.9772,0.0067,0.0026,0.0119</t>
+  </si>
+  <si>
+    <t>0.9828,0.0095,0.0017,0.0040</t>
+  </si>
+  <si>
+    <t>0.9847,0.0031,0.0008,0.0080</t>
+  </si>
+  <si>
+    <t>0.9967,0.0007,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.0892,0.0150,0.9606,0.0034</t>
+  </si>
+  <si>
+    <t>0.3399,0.1835,0.5414,0.0324</t>
+  </si>
+  <si>
+    <t>0.8570,0.0141,0.1130,0.0064</t>
+  </si>
+  <si>
+    <t>0.0516,0.0031,0.9700,0.0031</t>
+  </si>
+  <si>
+    <t>0.0015,0.0052,0.9855,0.0234</t>
+  </si>
+  <si>
+    <t>0.0285,0.0288,0.9631,0.0081</t>
+  </si>
+  <si>
+    <t>0.0202,0.0029,0.9922,0.0003</t>
+  </si>
+  <si>
+    <t>0.0087,0.0023,0.9893,0.0017</t>
+  </si>
+  <si>
+    <t>0.0012,0.0014,0.9971,0.0015</t>
+  </si>
+  <si>
+    <t>0.0017,0.0012,0.9923,0.0100</t>
+  </si>
+  <si>
+    <t>0.0371,0.0213,0.9269,0.0093</t>
+  </si>
+  <si>
+    <t>0.4802,0.0020,0.2818,0.1111</t>
+  </si>
+  <si>
+    <t>0.8838,0.0026,0.1333,0.0029</t>
+  </si>
+  <si>
+    <t>0.9146,0.0092,0.0194,0.0272</t>
+  </si>
+  <si>
+    <t>0.9929,0.0018,0.0005,0.0015</t>
+  </si>
+  <si>
+    <t>0.9900,0.0030,0.0022,0.0012</t>
+  </si>
+  <si>
+    <t>0.9910,0.0039,0.0014,0.0012</t>
+  </si>
+  <si>
+    <t>0.9916,0.0056,0.0005,0.0007</t>
+  </si>
+  <si>
+    <t>0.9978,0.0001,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9956,0.0009,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.9856,0.0074,0.0007,0.0022</t>
+  </si>
+  <si>
+    <t>0.9863,0.0041,0.0005,0.0031</t>
+  </si>
+  <si>
+    <t>0.0247,0.0370,0.9660,0.0010</t>
+  </si>
+  <si>
+    <t>0.0011,0.2590,0.9845,0.0007</t>
+  </si>
+  <si>
+    <t>0.0190,0.0179,0.9641,0.0131</t>
+  </si>
+  <si>
+    <t>0.0817,0.0368,0.8693,0.0102</t>
+  </si>
+  <si>
+    <t>0.0011,0.0014,0.9975,0.0011</t>
+  </si>
+  <si>
+    <t>0.1860,0.0005,0.7631,0.0297</t>
+  </si>
+  <si>
+    <t>0.1040,0.0027,0.9590,0.0017</t>
+  </si>
+  <si>
+    <t>0.1859,0.0099,0.8176,0.0257</t>
+  </si>
+  <si>
+    <t>0.4700,0.0015,0.0042,0.7048</t>
+  </si>
+  <si>
+    <t>0.0310,0.0086,0.0012,0.9829</t>
+  </si>
+  <si>
+    <t>0.0331,0.0003,0.0022,0.9844</t>
+  </si>
+  <si>
+    <t>0.0011,0.0003,0.0005,0.9992</t>
+  </si>
+  <si>
+    <t>0.0013,0.0001,0.0004,0.9992</t>
+  </si>
+  <si>
+    <t>0.9457,0.0088,0.0078,0.0230</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1967,10 +1970,10 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1987,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,10 +1998,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2057,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2071,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2085,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2113,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2127,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,10 +2138,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2152,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,10 +2166,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2183,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2197,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2205,10 +2208,10 @@
         <v>262</v>
       </c>
       <c r="C20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,10 +2222,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2239,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2253,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2267,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2278,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2289,10 +2292,10 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,10 +2306,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2317,10 +2320,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2331,10 +2334,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2345,10 +2348,10 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2365,7 @@
         <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2379,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2393,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2404,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2421,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2435,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2449,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,10 +2460,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2474,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2485,10 +2488,10 @@
         <v>261</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,10 +2502,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2513,10 +2516,10 @@
         <v>261</v>
       </c>
       <c r="C42" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,10 +2530,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2547,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2555,10 +2558,10 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2572,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2583,10 +2586,10 @@
         <v>262</v>
       </c>
       <c r="C47" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2603,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2617,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2625,10 +2628,10 @@
         <v>261</v>
       </c>
       <c r="C50" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2645,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2653,10 +2656,10 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2667,10 +2670,10 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2687,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2695,10 +2698,10 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2715,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2729,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2743,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2757,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2771,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2785,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2799,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2807,10 +2810,10 @@
         <v>262</v>
       </c>
       <c r="C63" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2821,10 +2824,10 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2835,10 +2838,10 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2849,10 +2852,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2869,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2877,10 +2880,10 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2911,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2925,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2939,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,10 +2950,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2964,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2981,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,10 +2992,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,10 +3006,10 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3017,10 +3020,10 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3031,10 +3034,10 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,10 +3048,10 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,10 +3062,10 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,10 +3076,10 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3087,10 +3090,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3101,10 +3104,10 @@
         <v>261</v>
       </c>
       <c r="C84" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3118,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3132,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3143,10 +3146,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,10 +3160,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3191,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3205,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3275,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3317,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3331,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3359,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3373,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3387,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3401,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3409,10 +3412,10 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3429,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3437,10 +3440,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3457,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3465,10 +3468,10 @@
         <v>262</v>
       </c>
       <c r="C110" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3479,10 +3482,10 @@
         <v>262</v>
       </c>
       <c r="C111" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3493,10 +3496,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3507,10 +3510,10 @@
         <v>262</v>
       </c>
       <c r="C113" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3521,10 +3524,10 @@
         <v>262</v>
       </c>
       <c r="C114" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3541,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3555,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3563,10 +3566,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3580,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3594,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3608,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3625,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3639,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3647,10 +3650,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3661,10 +3664,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3675,10 +3678,10 @@
         <v>262</v>
       </c>
       <c r="C125" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3695,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3709,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3751,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3765,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3779,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3793,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3821,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3832,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3846,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3863,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,10 +3874,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3891,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3905,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3916,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,10 +3944,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3955,10 +3958,10 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,10 +3972,10 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,10 +3986,10 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,10 +4000,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4028,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4059,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4073,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4087,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4115,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4129,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4157,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4196,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4241,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4269,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4283,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4297,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4311,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4353,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4367,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4381,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4395,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4409,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4423,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4437,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4451,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4465,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4479,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4487,10 +4490,10 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4501,10 +4504,10 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4515,10 +4518,10 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4529,10 +4532,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4543,10 +4546,10 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4557,10 +4560,10 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4577,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,7 +4591,7 @@
         <v>259</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4602,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4616,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4630,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4644,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4658,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4675,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4686,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4700,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4714,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4731,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4739,10 +4742,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4759,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4773,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4787,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4801,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4815,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4829,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4837,10 +4840,10 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4854,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,10 +4868,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4879,10 +4882,10 @@
         <v>261</v>
       </c>
       <c r="C211" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4896,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4941,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4955,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4983,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +4997,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5011,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,10 +5022,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5036,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5053,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5061,10 +5064,10 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5075,10 +5078,10 @@
         <v>261</v>
       </c>
       <c r="C225" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5089,10 +5092,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5103,10 +5106,10 @@
         <v>261</v>
       </c>
       <c r="C227" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,10 +5120,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5137,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5145,10 +5148,10 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,10 +5162,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5179,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5193,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5207,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5221,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5249,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5263,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5277,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5291,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5305,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5319,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,10 +5330,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5341,10 +5344,10 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5355,10 +5358,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5369,10 +5372,10 @@
         <v>261</v>
       </c>
       <c r="C246" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5383,10 +5386,10 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5400,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5411,10 +5414,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5425,10 +5428,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,10 +5442,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,10 +5456,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,10 +5470,10 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,10 +5484,10 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,10 +5498,10 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5515,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
